--- a/extenbooks/S506.xlsx
+++ b/extenbooks/S506.xlsx
@@ -447,11 +447,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B44"/>
+  <dimension ref="A1:D71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+    <col width="33" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,6 +467,16 @@
           <t>S&amp;T 1994, units=ratio</t>
         </is>
       </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>, units=ratio</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>BLS CES + BEA NIPA, units=ratio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -475,6 +487,16 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>S506-A</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>S506-COMBINED</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>S506-EXT</t>
         </is>
       </c>
     </row>
@@ -485,6 +507,12 @@
       <c r="B3" s="3" t="n">
         <v>1.7</v>
       </c>
+      <c r="C3" s="3" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -493,6 +521,12 @@
       <c r="B4" s="3" t="n">
         <v>1.75</v>
       </c>
+      <c r="C4" s="3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -501,6 +535,12 @@
       <c r="B5" s="3" t="n">
         <v>1.77</v>
       </c>
+      <c r="C5" s="3" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -509,6 +549,12 @@
       <c r="B6" s="3" t="n">
         <v>1.78</v>
       </c>
+      <c r="C6" s="3" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -517,6 +563,12 @@
       <c r="B7" s="3" t="n">
         <v>1.75</v>
       </c>
+      <c r="C7" s="3" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -525,6 +577,12 @@
       <c r="B8" s="3" t="n">
         <v>1.74</v>
       </c>
+      <c r="C8" s="3" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -533,6 +591,12 @@
       <c r="B9" s="3" t="n">
         <v>1.86</v>
       </c>
+      <c r="C9" s="3" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -541,6 +605,12 @@
       <c r="B10" s="3" t="n">
         <v>1.9</v>
       </c>
+      <c r="C10" s="3" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -549,6 +619,12 @@
       <c r="B11" s="3" t="n">
         <v>1.84</v>
       </c>
+      <c r="C11" s="3" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -557,6 +633,12 @@
       <c r="B12" s="3" t="n">
         <v>1.88</v>
       </c>
+      <c r="C12" s="3" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -565,6 +647,12 @@
       <c r="B13" s="3" t="n">
         <v>2.01</v>
       </c>
+      <c r="C13" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -573,6 +661,12 @@
       <c r="B14" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="C14" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -581,6 +675,12 @@
       <c r="B15" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="C15" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -589,6 +689,12 @@
       <c r="B16" s="3" t="n">
         <v>2.03</v>
       </c>
+      <c r="C16" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -597,6 +703,12 @@
       <c r="B17" s="3" t="n">
         <v>2.06</v>
       </c>
+      <c r="C17" s="3" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -605,6 +717,12 @@
       <c r="B18" s="3" t="n">
         <v>2.07</v>
       </c>
+      <c r="C18" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -613,6 +731,12 @@
       <c r="B19" s="3" t="n">
         <v>2.12</v>
       </c>
+      <c r="C19" s="3" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -621,6 +745,12 @@
       <c r="B20" s="3" t="n">
         <v>2.1</v>
       </c>
+      <c r="C20" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -629,6 +759,12 @@
       <c r="B21" s="3" t="n">
         <v>2.08</v>
       </c>
+      <c r="C21" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -637,6 +773,12 @@
       <c r="B22" s="3" t="n">
         <v>2.1</v>
       </c>
+      <c r="C22" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -645,6 +787,12 @@
       <c r="B23" s="3" t="n">
         <v>2.08</v>
       </c>
+      <c r="C23" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -653,6 +801,12 @@
       <c r="B24" s="3" t="n">
         <v>2.01</v>
       </c>
+      <c r="C24" s="3" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -661,6 +815,12 @@
       <c r="B25" s="3" t="n">
         <v>2.03</v>
       </c>
+      <c r="C25" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -669,6 +829,12 @@
       <c r="B26" s="3" t="n">
         <v>2.08</v>
       </c>
+      <c r="C26" s="3" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -677,6 +843,12 @@
       <c r="B27" s="3" t="n">
         <v>1.99</v>
       </c>
+      <c r="C27" s="3" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -685,6 +857,12 @@
       <c r="B28" s="3" t="n">
         <v>1.94</v>
       </c>
+      <c r="C28" s="3" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -693,6 +871,12 @@
       <c r="B29" s="3" t="n">
         <v>1.95</v>
       </c>
+      <c r="C29" s="3" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -701,6 +885,12 @@
       <c r="B30" s="3" t="n">
         <v>2.11</v>
       </c>
+      <c r="C30" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -709,6 +899,12 @@
       <c r="B31" s="3" t="n">
         <v>2.11</v>
       </c>
+      <c r="C31" s="3" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -717,6 +913,12 @@
       <c r="B32" s="3" t="n">
         <v>2.1</v>
       </c>
+      <c r="C32" s="3" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -725,6 +927,12 @@
       <c r="B33" s="3" t="n">
         <v>2.07</v>
       </c>
+      <c r="C33" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="D33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -733,6 +941,12 @@
       <c r="B34" s="3" t="n">
         <v>2.03</v>
       </c>
+      <c r="C34" s="3" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -741,6 +955,12 @@
       <c r="B35" s="3" t="n">
         <v>2.07</v>
       </c>
+      <c r="C35" s="3" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -749,6 +969,12 @@
       <c r="B36" s="3" t="n">
         <v>2.16</v>
       </c>
+      <c r="C36" s="3" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -757,6 +983,12 @@
       <c r="B37" s="3" t="n">
         <v>2.19</v>
       </c>
+      <c r="C37" s="3" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -765,6 +997,12 @@
       <c r="B38" s="3" t="n">
         <v>2.22</v>
       </c>
+      <c r="C38" s="3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -773,6 +1011,12 @@
       <c r="B39" s="3" t="n">
         <v>2.26</v>
       </c>
+      <c r="C39" s="3" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -781,6 +1025,12 @@
       <c r="B40" s="3" t="n">
         <v>2.33</v>
       </c>
+      <c r="C40" s="3" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -789,6 +1039,12 @@
       <c r="B41" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="C41" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -797,6 +1053,12 @@
       <c r="B42" s="3" t="n">
         <v>2.42</v>
       </c>
+      <c r="C42" s="3" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -805,6 +1067,12 @@
       <c r="B43" s="3" t="n">
         <v>2.4</v>
       </c>
+      <c r="C43" s="3" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -812,6 +1080,390 @@
       </c>
       <c r="B44" s="3" t="n">
         <v>2.44</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>1998</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>1.238017536625485</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>1.238017536625485</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>1999</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>1.217296200237947</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>1.217296200237947</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2000</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>1.203199180497708</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>1.203199180497708</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2001</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>1.202652710768182</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>1.202652710768182</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2002</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>1.259854095506723</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>1.259854095506723</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2003</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>1.365336224004371</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>1.365336224004371</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2004</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1.435207093530869</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1.435207093530869</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2005</v>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>1.500540719674654</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>1.500540719674654</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2006</v>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>1.542032830911822</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>1.542032830911822</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2007</v>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>1.537926674935985</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>1.537926674935985</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2008</v>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>1.542987227477646</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>1.542987227477646</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2009</v>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>1.626140113334551</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>1.626140113334551</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2010</v>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>1.758565095484922</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>1.758565095484922</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2011</v>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>1.777655825543303</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>1.777655825543303</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2012</v>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>1.746394801908146</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>1.746394801908146</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2013</v>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>1.800931957654951</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>1.800931957654951</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2014</v>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>1.762626966439078</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>1.762626966439078</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2015</v>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>1.698020520307816</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>1.698020520307816</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>1.66340931886333</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>1.66340931886333</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>1.668365819576659</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>1.668365819576659</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>1.668349187278784</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>1.668349187278784</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>1.625429932610544</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>1.625429932610544</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1.584738121234693</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1.584738121234693</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>1.772731893535499</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>1.772731893535499</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>1.880615019880321</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>1.880615019880321</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B70" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>1.853577620273632</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>1.853577620273632</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2024</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>1.790828883774963</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1.790828883774963</v>
       </c>
     </row>
   </sheetData>
@@ -825,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -924,7 +1576,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1948–2024</t>
+          <t>1948-1989</t>
         </is>
       </c>
     </row>
@@ -948,7 +1600,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fig_5_3, Fig_9_3, Fig_9_5</t>
+          <t>Fig_5_3, Fig_9_3, Fig_9_5, Fig_5_8</t>
         </is>
       </c>
     </row>
@@ -990,386 +1642,391 @@
     </row>
     <row r="14"/>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Subseries</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>source / role</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>S506-A</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>S&amp;T 1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>S506-EXT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>BLS CES + BEA NIPA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>S506-COMBINED</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
+    </row>
+    <row r="19"/>
+    <row r="20">
+      <c r="A20" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t># S506 — Rate of Exploitation (e = S*/V*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr"/>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix H.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>**Units**: ratio</t>
-        </is>
-      </c>
+      <c r="B20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+          <t># S506 — Rate of Exploitation (e = S*/V*)</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>**Content Type**: time_series</t>
-        </is>
-      </c>
+      <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>**Source Table**: Appendix H.1</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Units**: ratio</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr"/>
-      <c r="B28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>**Status**: book_period_validated</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Rate of Exploitation: e = S*/V*. The book's central Marxian magnitude. Identity-checked against S505/S504 ratio.</t>
-        </is>
-      </c>
+      <c r="B29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
-      <c r="B30" t="inlineStr"/>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Rate of Exploitation: e = S*/V*. The book's central Marxian magnitude. Identity-checked against S505/S504 ratio.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>| `S506-A` | S&amp;T 1994 | 1948-1989 | ratio |</t>
-        </is>
-      </c>
+      <c r="B37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>| `S506-EXT` | BLS CES + BEA NIPA | 1990-2024 | ratio |</t>
+          <t>## Subseries</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>| `S506-COMBINED` |  | 1948-2024 | ratio |</t>
-        </is>
-      </c>
+      <c r="B39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr"/>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>| Subseries | Source | Period | Units |</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr"/>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>| `S506-A` | S&amp;T 1994 | 1948-1989 | ratio |</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>| `S506-EXT` | BLS CES + BEA NIPA | 1990-2024 | ratio |</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr"/>
-      <c r="B44" t="inlineStr"/>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>| `S506-COMBINED` |  | 1948-2024 | ratio |</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>### S506-A (book period, 1948-1989)</t>
-        </is>
-      </c>
+      <c r="B45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
-      <c r="B46" t="inlineStr"/>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
-        </is>
-      </c>
+      <c r="B47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2. Extract column `S_star_V_star` (and the `year` index).</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
-        </is>
-      </c>
+      <c r="B49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr"/>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>### S506-A (book period, 1948-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
-        </is>
-      </c>
+      <c r="B51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr"/>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>2. Extract column `S_star_V_star` (and the `year` index).</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr"/>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>3. No further transformation — this is the canonical published value.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
-      <c r="B56" t="inlineStr"/>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>1948=1.70, 1958=2.01, 1967=2.10, 1972=1.99, 1977=2.10, 1989=2.44</t>
-        </is>
-      </c>
+      <c r="B57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr"/>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Tolerance class: `rate_series` (rel 0.001 / abs 0.01).</t>
-        </is>
-      </c>
+      <c r="B59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr"/>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S506_exploitation_rate.py` writes to `data/intermediate/validation/S506.json`.</t>
-        </is>
-      </c>
+      <c r="B61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr"/>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>1948=1.70, 1958=2.01, 1967=2.10, 1972=1.99, 1977=2.10, 1989=2.44</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr"/>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Tolerance class: `rate_series` (rel 0.001 / abs 0.01).</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr"/>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S506_exploitation_rate.py` writes to `data/intermediate/validation/S506.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
+          <t>---</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S506_exploitation_rate.py</t>
-        </is>
-      </c>
+      <c r="B69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S506.csv</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S506_exploitation_rate.py</t>
-        </is>
-      </c>
+      <c r="B71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S506.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -1377,7 +2034,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S506_exploitation_rate.py</t>
+          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
         </is>
       </c>
     </row>
@@ -1385,65 +2042,105 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S506_exploitation_rate.py</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
-      <c r="B75" t="inlineStr"/>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t xml:space="preserve">       └── data/intermediate/S506.csv</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>---</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S506_exploitation_rate.py</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr"/>
-      <c r="B77" t="inlineStr"/>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                 └── data/final/S506.csv</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S506_exploitation_rate.py</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr"/>
-      <c r="B79" t="inlineStr"/>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
-        </is>
-      </c>
+      <c r="B80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
-      <c r="B81" t="inlineStr"/>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr"/>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr">
+      <c r="B84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr"/>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr"/>
+      <c r="B86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr"/>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr"/>
+      <c r="B88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr"/>
+      <c r="B89" t="inlineStr">
         <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
         </is>
@@ -1460,10 +2157,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="29" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1488,212 +2185,282 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>methodology_description</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>e = S*/V*. The rate of exploitation measures how much surplus value is extracted per unit of variable capital. Under the approximation ec_u/ec_p ≈ 1, this simplifies to e = (GFP/W)(1/(V*/W)) - 1. For extension: e = 1.238/(V*/W) - 1, using the empirical constant derived from book-period GFP/W stability.</t>
+          <t>Figure 5.13 is the pièce de résistance. It compares the rate of surplus value S*/V* (which is the rate of exploitation of productive workers) with its 'naive' equivalent (P+)/EC. At midperiod, the former is almost four times as large as the latter. It also rises by over 40% during the postwar period, whereas the latter actually falls by almost 30%. Thus P+/EC grossly understates the level, and falsifies the trend, of S*/V*. The profit/wage ratio is not a good proxy for the rate of surplus value.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/equations/page_340_equations.txt</t>
+          <t>ST_1994, Ch5, p.114; chunk_14</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>benchmark_values</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Book benchmarks from Table 5.7: 1948=1.70, 1958=1.83, 1967=2.10, 1977=2.10, 1989=2.44. The rising trend reflects the secular decline in productive labor's share of total employment and compensation.</t>
+          <t>The rate of exploitation is the ratio of surplus labor time to necessary labor time. This can be calculated for any capitalistically employed wage labor, be it productive or unproductive. Necessary labor time is simply the value of the labor power involved, that is, the labor value of the average annual consumption per worker in the activities in question. Surplus labor time is excess of working time over necessary labor time. In the case of productive workers, their rate of exploitation is also the rate of surplus value, since their surplus labor time results in surplus value.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ST_1994, Table 5.7</t>
+          <t>ST_1994, Ch5, p.129; chunk_15</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>figure_context</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fig 5.3 plots the rate of exploitation over time, showing the secular rise. Figs 9.3 and 9.5 use the exploitation rate in the context of profit rate decomposition and long-run distributional dynamics.</t>
+          <t>Because the rate of exploitation of productive workers is simply the rate of surplus value, we can directly estimate the rate of exploitation of unproductive workers. We use the money rate of surplus value S*/V* since we already know that it is quite close to the value rate, as shown in Section 4.2.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ST_1994, Figs 5.3, 9.3, 9.5</t>
+          <t>ST_1994, Ch5, p.130; chunk_15</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>extension_formula</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>The extension formula e = 1.238/(V*/W) - 1 derives from the observation that GFP/W ≈ 1.238 is approximately constant over the book period. Since e = S*/V* = (GFP - V*)/V* = (GFP/W)/(V*/W) - 1, and GFP/W is stable, the exploitation rate is driven primarily by changes in the productive wage share V*/W.</t>
+          <t>The main period is from 1948 to 1980, during which the rate of surplus value rises modestly by almost 22%, the adjusted value composition rises by over 77%, and the adjusted materialized composition rises by over 56%. Because the large rise in the value composition overwhelms the modest one in the rate of surplus value, the adjusted Marxian rate of profit falls by almost a third over this period.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; DPR T506_DPR.md</t>
+          <t>ST_1994, Ch5, p.124; chunk_15</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>external_comparison</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mohun (2013) reports exploitation rates of ~2.3-2.5 for the overlapping period, compared to ST's 2.6-2.7. The difference arises from Mohun's broader productive sector (Information entirely productive, retail eating/drinking productive). Detailed comparison in detailed_exploitation_comparison_ST_vs_Mohun.csv.</t>
+          <t>Figure 5.13 is the pièce de résistance. It compares the rate of surplus value S*/V* (which is the rate of exploitation of productive workers) with its 'naive' equivalent (P⁺)/EC. At midperiod, the former is almost four times as large as the latter. It also rises by over 40% during the postwar period, whereas the latter actually falls by almost 30%. Thus P⁺/EC grossly understates the level, and falsifies the trend, of S*/V*. The profit/wage ratio is not a good proxy for the rate of surplus value.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Mohun_2013; Inputs/ExternalSources/Mohun/detailed_exploitation_comparison_ST_vs_Mohun.csv</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>caveat</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>The 1.238 constant for GFP/W assumes stability that may not hold post-1989 if the sectoral composition of value-added shifts significantly. The extension should be validated against any available independent estimates of the exploitation rate.</t>
+          <t>S* = VA* − V* = surplus value (in money form); S*/V* = rate of surplus value.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CHAPTER_5_INVESTIGATION.md</t>
+          <t>ST_1994</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>decision_reference</t>
+          <t>verbatim_quote</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DEC-003: The VA*/W constant assumption (ec_u/ec_p ≈ 1.238) affects S506 extension period values. Initially used constant VA*/W = 1.238; partially resolved in Session 14 by enabling year-varying ec_u/ec_p input. Full resolution requires BLS industry-level compensation data unavailable for 1990-1997 (SIC-era gap). Extension period values carry small systematic error; see ADJ-002. DEC-007 further documents the log-linear interpolation used for the 1990-1997 gap.</t>
+          <t>We use the money rate of surplus value S*/V* since we already know that it is quite close to the value rate, as shown in Section 4.2.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>DECISION_LOG.md DEC-003 (2025-12-05, partially resolved 2026-03-30)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
+          <t>ST_1994</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>methodology_description</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>e = S*/V*. The rate of exploitation measures how much surplus value is extracted per unit of variable capital. Under the approximation ec_u/ec_p ≈ 1, this simplifies to e = (GFP/W)(1/(V*/W)) - 1. For extension: e = 1.238/(V*/W) - 1, using the empirical constant derived from book-period GFP/W stability.</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; Knowledge_Base/equations/page_340_equations.txt</t>
+        </is>
+      </c>
+    </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>methodology_summary</t>
+          <t>benchmark_values</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Rate of exploitation e = S*/V*, rising from 1.70 (1948) to 2.44 (1989). Extended via e = 1.238/(V*/W) - 1. Mohun comparison shows classification sensitivity (~2.3-2.5 vs ST's 2.6-2.7). DEC-003: VA*/W constant assumption partially resolved; 1990-1997 values interpolated (DEC-007).</t>
-        </is>
-      </c>
-    </row>
-    <row r="11"/>
+          <t>Book benchmarks from Table 5.7: 1948=1.70, 1958=1.83, 1967=2.10, 1977=2.10, 1989=2.44. The rising trend reflects the secular decline in productive labor's share of total employment and compensation.</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ST_1994, Table 5.7</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>figure_context</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Fig 5.3 plots the rate of exploitation over time, showing the secular rise. Figs 9.3 and 9.5 use the exploitation rate in the context of profit rate decomposition and long-run distributional dynamics.</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ST_1994, Figs 5.3, 9.3, 9.5</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>known_issues:</t>
+          <t>extension_formula</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>The extension formula e = 1.238/(V*/W) - 1 derives from the observation that GFP/W ≈ 1.238 is approximately constant over the book period. Since e = S*/V* = (GFP - V*)/V* = (GFP/W)/(V*/W) - 1, and GFP/W is stable, the exploitation rate is driven primarily by changes in the productive wage share V*/W.</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ST_1994, Ch5; DPR T506_DPR.md</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>external_comparison</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GFP/W ≈ 1.238 constancy assumption may weaken post-1989</t>
+          <t>Mohun (2013) reports exploitation rates of ~2.3-2.5 for the overlapping period, compared to ST's 2.6-2.7. The difference arises from Mohun's broader productive sector (Information entirely productive, retail eating/drinking productive). Detailed comparison in detailed_exploitation_comparison_ST_vs_Mohun.csv.</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Mohun_2013; Inputs/ExternalSources/Mohun/detailed_exploitation_comparison_ST_vs_Mohun.csv</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>caveat</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Classification-sensitive: Mohun's broader productive sector yields lower e</t>
+          <t>The 1.238 constant for GFP/W assumes stability that may not hold post-1989 if the sectoral composition of value-added shifts significantly. The extension should be validated against any available independent estimates of the exploitation rate.</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CHAPTER_5_INVESTIGATION.md</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>decision_reference</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Extension validity depends on S512 quality</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DEC-003: VA*/W constant carries small systematic error for 1990-1997 (interpolated per DEC-007) and post-1997 extension period</t>
-        </is>
-      </c>
-    </row>
-    <row r="17"/>
+          <t>[internal-decision-record]: The VA*/W constant assumption (ec_u/ec_p ≈ 1.238) affects S506 extension period values. Initially used constant VA*/W = 1.238; partially resolved in Session 14 by enabling year-varying ec_u/ec_p input. Full resolution requires BLS industry-level compensation data unavailable for 1990-1997 (SIC-era gap). Extension period values carry small systematic error; see ADJ-002. [internal-decision-record] further documents the log-linear interpolation used for the 1990-1997 gap.</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[internal-decision-log] [internal-decision-record] (2025-12-05, partially resolved 2026-03-30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>VERBATIM QUOTES (top-level)</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr"/>
+      <c r="C17" s="4" t="inlineStr"/>
+    </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>cross_references:</t>
-        </is>
+      <c r="A18" t="inlineStr"/>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>S504</t>
-        </is>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="n">
+        <v>114</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr"/>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>S505</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>S507</t>
-        </is>
-      </c>
-    </row>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="n">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="21"/>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>methodology_summary</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S512</t>
+          <t>Rate of exploitation e = S*/V*, rising from 1.70 (1948) to 2.44 (1989). Extended via e = 1.238/(V*/W) - 1. Mohun comparison shows classification sensitivity (~2.3-2.5 vs ST's 2.6-2.7). [internal-decision-record]: VA*/W constant assumption partially resolved; 1990-1997 values interpolated ([internal-decision-record]).</t>
         </is>
       </c>
     </row>
@@ -1701,29 +2468,109 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
+          <t>known_issues:</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>GFP/W ≈ 1.238 constancy assumption may weaken post-1989</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr"/>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Classification-sensitive: Mohun's broader productive sector yields lower e</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr"/>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Extension validity depends on S512 quality</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr"/>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>[internal-decision-record]: VA*/W constant carries small systematic error for 1990-1997 (interpolated per [internal-decision-record]) and post-1997 extension period</t>
+        </is>
+      </c>
+    </row>
+    <row r="29"/>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>cross_references:</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>S504</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr"/>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>S505</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>S507</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr"/>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>S512</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
           <t>citations:</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
+    <row r="37">
+      <c r="A37" t="inlineStr">
         <is>
           <t>ST_1994</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. Measuring the Wealth of Nations: The Political Economy of National Accounts. Cambridge University Press.</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>Mohun_2013</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>Mohun, Simon. 2013. 'Unproductive Labor in the U.S. Economy 1964-2010.' Review of Radical Political Economics 46(3): 355-379.</t>
         </is>
@@ -1740,10 +2587,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="20" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -1840,91 +2687,178 @@
     </row>
     <row r="5"/>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" s="4" t="inlineStr"/>
+      <c r="C6" s="4" t="n"/>
+      <c r="D6" s="4" t="n"/>
+      <c r="E6" s="4" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>['S512']</t>
-        </is>
-      </c>
-    </row>
-    <row r="10"/>
+          <t>derive</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>output_subseries</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>S506-EXT</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
+          <t>combined_subseries</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>S506-COMBINED</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>reference_values</t>
+          <t>provenance</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"1948": 1.7, "1958": 2.01, "1967": 2.1, "1972": 1.99, "1977": 2.1, "1989": 2.44}</t>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.7 (rate of surplus value e = S*/V*); identity from Appendix H.1 series", "shaikh_appendix_ref": "Table 5.7 (rate of surplus value, 1948-1989); Appendix H.1 (S_star, V_star); Figure 5.6", "extension_source": "Derived ratio: e = S505 / S504. Inherits sources from S505 and S504 (which in turn depend on BLS CES + BEA NIPA).", "extension_url": "n/a (derived from S505 and S504)", "conceptual_continuity": "Rate of exploitation e = S*/V* is the Marxian ratio of surplus value to variable capital -- the rate at which capital extracts value from productive labor. It is a pure ratio of two derived/aggregate series, and per the Anu Extension Standard must be recomputed from extended components, NOT growth-rate spliced. Conceptual continuity holds as long as the numerator and denominator are extended with their Marxian definitions intact.", "vintage_note": "Inherits vintage divergences from S505 and S504. As a ratio, dimensionless, so unit-vintage issues cancel.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>["S512"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>reference_values</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>{"1948": 1.7, "1958": 2.01, "1967": 2.1, "1972": 1.99, "1977": 2.1, "1989": 2.44}</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
           <t>expected_range</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>[1.0, 5.0]</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+    <row r="18">
+      <c r="A18" t="inlineStr">
         <is>
           <t>tolerance</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>tolerance_class</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>rate_series</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0.01</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S506.xlsx
+++ b/extenbooks/S506.xlsx
@@ -1096,10 +1096,10 @@
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1.238017536625485</v>
+        <v>1.269989215720135</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1.238017536625485</v>
+        <v>1.269989215720135</v>
       </c>
     </row>
     <row r="46">
@@ -1110,10 +1110,10 @@
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1.217296200237947</v>
+        <v>1.248971860241347</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1.217296200237947</v>
+        <v>1.248971860241347</v>
       </c>
     </row>
     <row r="47">
@@ -1124,10 +1124,10 @@
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1.203199180497708</v>
+        <v>1.234673454504817</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>1.203199180497708</v>
+        <v>1.234673454504817</v>
       </c>
     </row>
     <row r="48">
@@ -1138,10 +1138,10 @@
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.202652710768182</v>
+        <v>1.23411917806487</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.202652710768182</v>
+        <v>1.23411917806487</v>
       </c>
     </row>
     <row r="49">
@@ -1152,10 +1152,10 @@
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1.259854095506723</v>
+        <v>1.292137725442533</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1.259854095506723</v>
+        <v>1.292137725442533</v>
       </c>
     </row>
     <row r="50">
@@ -1166,10 +1166,10 @@
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1.365336224004371</v>
+        <v>1.399126741490147</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1.365336224004371</v>
+        <v>1.399126741490147</v>
       </c>
     </row>
     <row r="51">
@@ -1180,10 +1180,10 @@
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1.435207093530869</v>
+        <v>1.469995766295596</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1.435207093530869</v>
+        <v>1.469995766295596</v>
       </c>
     </row>
     <row r="52">
@@ -1194,10 +1194,10 @@
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1.500540719674654</v>
+        <v>1.53626272995572</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1.500540719674654</v>
+        <v>1.53626272995572</v>
       </c>
     </row>
     <row r="53">
@@ -1208,10 +1208,10 @@
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1.542032830911822</v>
+        <v>1.578347585639134</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>1.542032830911822</v>
+        <v>1.578347585639134</v>
       </c>
     </row>
     <row r="54">
@@ -1222,10 +1222,10 @@
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1.537926674935985</v>
+        <v>1.574182770292213</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1.537926674935985</v>
+        <v>1.574182770292213</v>
       </c>
     </row>
     <row r="55">
@@ -1236,10 +1236,10 @@
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1.542987227477646</v>
+        <v>1.579315616441613</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>1.542987227477646</v>
+        <v>1.579315616441613</v>
       </c>
     </row>
     <row r="56">
@@ -1250,10 +1250,10 @@
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1.626140113334551</v>
+        <v>1.663656400667903</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1.626140113334551</v>
+        <v>1.663656400667903</v>
       </c>
     </row>
     <row r="57">
@@ -1264,10 +1264,10 @@
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1.758565095484922</v>
+        <v>1.797973168277564</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>1.758565095484922</v>
+        <v>1.797973168277564</v>
       </c>
     </row>
     <row r="58">
@@ -1278,10 +1278,10 @@
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1.777655825543303</v>
+        <v>1.817336623051065</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>1.777655825543303</v>
+        <v>1.817336623051065</v>
       </c>
     </row>
     <row r="59">
@@ -1292,10 +1292,10 @@
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1.746394801908146</v>
+        <v>1.785629013363977</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1.746394801908146</v>
+        <v>1.785629013363977</v>
       </c>
     </row>
     <row r="60">
@@ -1306,10 +1306,10 @@
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1.800931957654951</v>
+        <v>1.840945271335736</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1.800931957654951</v>
+        <v>1.840945271335736</v>
       </c>
     </row>
     <row r="61">
@@ -1320,10 +1320,10 @@
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1.762626966439078</v>
+        <v>1.802093065959636</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.762626966439078</v>
+        <v>1.802093065959636</v>
       </c>
     </row>
     <row r="62">
@@ -1334,10 +1334,10 @@
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1.698020520307816</v>
+        <v>1.736563670597928</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>1.698020520307816</v>
+        <v>1.736563670597928</v>
       </c>
     </row>
     <row r="63">
@@ -1348,10 +1348,10 @@
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1.66340931886333</v>
+        <v>1.701458023418519</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1.66340931886333</v>
+        <v>1.701458023418519</v>
       </c>
     </row>
     <row r="64">
@@ -1362,10 +1362,10 @@
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1.668365819576659</v>
+        <v>1.706485331284896</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1.668365819576659</v>
+        <v>1.706485331284896</v>
       </c>
     </row>
     <row r="65">
@@ -1376,10 +1376,10 @@
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1.668349187278784</v>
+        <v>1.706468461382766</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>1.668349187278784</v>
+        <v>1.706468461382766</v>
       </c>
     </row>
     <row r="66">
@@ -1390,10 +1390,10 @@
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1.625429932610544</v>
+        <v>1.66293607450498</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1.625429932610544</v>
+        <v>1.66293607450498</v>
       </c>
     </row>
     <row r="67">
@@ -1404,10 +1404,10 @@
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1.584738121234693</v>
+        <v>1.621662951538046</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>1.584738121234693</v>
+        <v>1.621662951538046</v>
       </c>
     </row>
     <row r="68">
@@ -1418,10 +1418,10 @@
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>1.772731893535499</v>
+        <v>1.812342349157434</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1.772731893535499</v>
+        <v>1.812342349157434</v>
       </c>
     </row>
     <row r="69">
@@ -1432,10 +1432,10 @@
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>1.880615019880321</v>
+        <v>1.921766663021468</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>1.880615019880321</v>
+        <v>1.921766663021468</v>
       </c>
     </row>
     <row r="70">
@@ -1446,10 +1446,10 @@
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>1.853577620273632</v>
+        <v>1.894343014848968</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>1.853577620273632</v>
+        <v>1.894343014848968</v>
       </c>
     </row>
     <row r="71">
@@ -1460,10 +1460,10 @@
         <v/>
       </c>
       <c r="C71" s="3" t="n">
-        <v>1.790828883774963</v>
+        <v>1.830697867828891</v>
       </c>
       <c r="D71" s="3" t="n">
-        <v>1.790828883774963</v>
+        <v>1.830697867828891</v>
       </c>
     </row>
   </sheetData>
@@ -2587,10 +2587,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -2862,6 +2862,18 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/extenbooks/S506.xlsx
+++ b/extenbooks/S506.xlsx
@@ -447,13 +447,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D71"/>
+  <dimension ref="A1:F79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
+    <col width="50" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -477,6 +479,16 @@
           <t>BLS CES + BEA NIPA, units=ratio</t>
         </is>
       </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>BEA GDP-by-Industry + SIC partition A (I-O uplift kIO held), units=ratio</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>pre-review S512 level-splice hybrid, units=ratio</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -497,6 +509,16 @@
       <c r="D2" s="2" t="inlineStr">
         <is>
           <t>S506-EXT</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>S506-EXT-MARX</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>S506-EXT-OLD-DEPRECATED</t>
         </is>
       </c>
     </row>
@@ -513,6 +535,12 @@
       <c r="D3" s="3" t="n">
         <v/>
       </c>
+      <c r="E3" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -527,6 +555,12 @@
       <c r="D4" s="3" t="n">
         <v/>
       </c>
+      <c r="E4" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -541,6 +575,12 @@
       <c r="D5" s="3" t="n">
         <v/>
       </c>
+      <c r="E5" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -555,6 +595,12 @@
       <c r="D6" s="3" t="n">
         <v/>
       </c>
+      <c r="E6" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -569,6 +615,12 @@
       <c r="D7" s="3" t="n">
         <v/>
       </c>
+      <c r="E7" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -583,6 +635,12 @@
       <c r="D8" s="3" t="n">
         <v/>
       </c>
+      <c r="E8" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -597,6 +655,12 @@
       <c r="D9" s="3" t="n">
         <v/>
       </c>
+      <c r="E9" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -611,6 +675,12 @@
       <c r="D10" s="3" t="n">
         <v/>
       </c>
+      <c r="E10" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -625,6 +695,12 @@
       <c r="D11" s="3" t="n">
         <v/>
       </c>
+      <c r="E11" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -639,6 +715,12 @@
       <c r="D12" s="3" t="n">
         <v/>
       </c>
+      <c r="E12" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -653,6 +735,12 @@
       <c r="D13" s="3" t="n">
         <v/>
       </c>
+      <c r="E13" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -667,6 +755,12 @@
       <c r="D14" s="3" t="n">
         <v/>
       </c>
+      <c r="E14" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -681,6 +775,12 @@
       <c r="D15" s="3" t="n">
         <v/>
       </c>
+      <c r="E15" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -695,6 +795,12 @@
       <c r="D16" s="3" t="n">
         <v/>
       </c>
+      <c r="E16" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -709,6 +815,12 @@
       <c r="D17" s="3" t="n">
         <v/>
       </c>
+      <c r="E17" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -723,6 +835,12 @@
       <c r="D18" s="3" t="n">
         <v/>
       </c>
+      <c r="E18" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -737,6 +855,12 @@
       <c r="D19" s="3" t="n">
         <v/>
       </c>
+      <c r="E19" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -751,6 +875,12 @@
       <c r="D20" s="3" t="n">
         <v/>
       </c>
+      <c r="E20" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -765,6 +895,12 @@
       <c r="D21" s="3" t="n">
         <v/>
       </c>
+      <c r="E21" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -779,6 +915,12 @@
       <c r="D22" s="3" t="n">
         <v/>
       </c>
+      <c r="E22" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -793,6 +935,12 @@
       <c r="D23" s="3" t="n">
         <v/>
       </c>
+      <c r="E23" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -807,6 +955,12 @@
       <c r="D24" s="3" t="n">
         <v/>
       </c>
+      <c r="E24" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -821,6 +975,12 @@
       <c r="D25" s="3" t="n">
         <v/>
       </c>
+      <c r="E25" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -835,6 +995,12 @@
       <c r="D26" s="3" t="n">
         <v/>
       </c>
+      <c r="E26" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -849,6 +1015,12 @@
       <c r="D27" s="3" t="n">
         <v/>
       </c>
+      <c r="E27" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -863,6 +1035,12 @@
       <c r="D28" s="3" t="n">
         <v/>
       </c>
+      <c r="E28" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -877,6 +1055,12 @@
       <c r="D29" s="3" t="n">
         <v/>
       </c>
+      <c r="E29" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -891,6 +1075,12 @@
       <c r="D30" s="3" t="n">
         <v/>
       </c>
+      <c r="E30" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -905,6 +1095,12 @@
       <c r="D31" s="3" t="n">
         <v/>
       </c>
+      <c r="E31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -919,6 +1115,12 @@
       <c r="D32" s="3" t="n">
         <v/>
       </c>
+      <c r="E32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -933,6 +1135,12 @@
       <c r="D33" s="3" t="n">
         <v/>
       </c>
+      <c r="E33" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -947,6 +1155,12 @@
       <c r="D34" s="3" t="n">
         <v/>
       </c>
+      <c r="E34" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -961,6 +1175,12 @@
       <c r="D35" s="3" t="n">
         <v/>
       </c>
+      <c r="E35" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -975,6 +1195,12 @@
       <c r="D36" s="3" t="n">
         <v/>
       </c>
+      <c r="E36" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -989,6 +1215,12 @@
       <c r="D37" s="3" t="n">
         <v/>
       </c>
+      <c r="E37" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1003,6 +1235,12 @@
       <c r="D38" s="3" t="n">
         <v/>
       </c>
+      <c r="E38" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1017,6 +1255,12 @@
       <c r="D39" s="3" t="n">
         <v/>
       </c>
+      <c r="E39" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1031,6 +1275,12 @@
       <c r="D40" s="3" t="n">
         <v/>
       </c>
+      <c r="E40" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1045,6 +1295,12 @@
       <c r="D41" s="3" t="n">
         <v/>
       </c>
+      <c r="E41" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1059,6 +1315,12 @@
       <c r="D42" s="3" t="n">
         <v/>
       </c>
+      <c r="E42" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1073,6 +1335,12 @@
       <c r="D43" s="3" t="n">
         <v/>
       </c>
+      <c r="E43" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1087,382 +1355,710 @@
       <c r="D44" s="3" t="n">
         <v/>
       </c>
+      <c r="E44" s="3" t="n">
+        <v/>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1998</v>
+        <v>1990</v>
       </c>
       <c r="B45" s="3" t="n">
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>1.269989215720135</v>
+        <v>2.467315213499074</v>
       </c>
       <c r="D45" s="3" t="n">
-        <v>1.269989215720135</v>
+        <v>0.7159641560036654</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>2.467315213499074</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1999</v>
+        <v>1991</v>
       </c>
       <c r="B46" s="3" t="n">
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>1.248971860241347</v>
+        <v>2.51833159492349</v>
       </c>
       <c r="D46" s="3" t="n">
-        <v>1.248971860241347</v>
+        <v>0.7095017617597911</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>2.51833159492349</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2000</v>
+        <v>1992</v>
       </c>
       <c r="B47" s="3" t="n">
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>1.234673454504817</v>
+        <v>2.580312523206792</v>
       </c>
       <c r="D47" s="3" t="n">
-        <v>1.234673454504817</v>
+        <v>0.7104278671342835</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>2.580312523206792</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2001</v>
+        <v>1993</v>
       </c>
       <c r="B48" s="3" t="n">
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>1.23411917806487</v>
+        <v>2.740840029977277</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.23411917806487</v>
+        <v>0.7262851098059526</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>2.740840029977277</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2002</v>
+        <v>1994</v>
       </c>
       <c r="B49" s="3" t="n">
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>1.292137725442533</v>
+        <v>3.010901925958908</v>
       </c>
       <c r="D49" s="3" t="n">
-        <v>1.292137725442533</v>
+        <v>0.7593407911191818</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>3.010901925958908</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2003</v>
+        <v>1995</v>
       </c>
       <c r="B50" s="3" t="n">
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>1.399126741490147</v>
+        <v>3.161125328931637</v>
       </c>
       <c r="D50" s="3" t="n">
-        <v>1.399126741490147</v>
+        <v>0.7651076185758044</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>3.161125328931637</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2004</v>
+        <v>1996</v>
       </c>
       <c r="B51" s="3" t="n">
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>1.469995766295596</v>
+        <v>3.355580194486014</v>
       </c>
       <c r="D51" s="3" t="n">
-        <v>1.469995766295596</v>
+        <v>0.8021141813675748</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>3.355580194486014</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2005</v>
+        <v>1997</v>
       </c>
       <c r="B52" s="3" t="n">
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>1.53626272995572</v>
+        <v>3.503306012029305</v>
       </c>
       <c r="D52" s="3" t="n">
-        <v>1.53626272995572</v>
+        <v>0.8021295418354709</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>3.503306012029305</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v/>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2006</v>
+        <v>1998</v>
       </c>
       <c r="B53" s="3" t="n">
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>1.578347585639134</v>
+        <v>2.970693723369081</v>
       </c>
       <c r="D53" s="3" t="n">
-        <v>1.578347585639134</v>
+        <v>0.7891049047666041</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>2.970693723369081</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>1.269989215720135</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2007</v>
+        <v>1999</v>
       </c>
       <c r="B54" s="3" t="n">
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>1.574182770292213</v>
+        <v>2.934462920074003</v>
       </c>
       <c r="D54" s="3" t="n">
-        <v>1.574182770292213</v>
+        <v>0.7764347622394002</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>2.934462920074003</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>1.248971860241347</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2008</v>
+        <v>2000</v>
       </c>
       <c r="B55" s="3" t="n">
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>1.579315616441613</v>
+        <v>2.909339725853235</v>
       </c>
       <c r="D55" s="3" t="n">
-        <v>1.579315616441613</v>
+        <v>0.7612719298245614</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>2.909339725853235</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>1.234673454504817</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2009</v>
+        <v>2001</v>
       </c>
       <c r="B56" s="3" t="n">
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>1.663656400667903</v>
+        <v>2.908468356161119</v>
       </c>
       <c r="D56" s="3" t="n">
-        <v>1.663656400667903</v>
+        <v>0.748118985126859</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>2.908468356161119</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>1.23411917806487</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2010</v>
+        <v>2002</v>
       </c>
       <c r="B57" s="3" t="n">
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>1.797973168277564</v>
+        <v>3.00986818445747</v>
       </c>
       <c r="D57" s="3" t="n">
-        <v>1.797973168277564</v>
+        <v>0.7698707735882457</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>3.00986818445747</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>1.292137725442533</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2011</v>
+        <v>2003</v>
       </c>
       <c r="B58" s="3" t="n">
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>1.817336623051065</v>
+        <v>3.196929936513684</v>
       </c>
       <c r="D58" s="3" t="n">
-        <v>1.817336623051065</v>
+        <v>0.8375435540069687</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>3.196929936513684</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>1.399126741490147</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2012</v>
+        <v>2004</v>
       </c>
       <c r="B59" s="3" t="n">
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>1.785629013363977</v>
+        <v>3.320905184104303</v>
       </c>
       <c r="D59" s="3" t="n">
-        <v>1.785629013363977</v>
+        <v>0.8922743922743922</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>3.320905184104303</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>1.469995766295596</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2013</v>
+        <v>2005</v>
       </c>
       <c r="B60" s="3" t="n">
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>1.840945271335736</v>
+        <v>3.436829782324695</v>
       </c>
       <c r="D60" s="3" t="n">
-        <v>1.840945271335736</v>
+        <v>0.9392333439591968</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>3.436829782324695</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>1.53626272995572</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2014</v>
+        <v>2006</v>
       </c>
       <c r="B61" s="3" t="n">
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>1.802093065959636</v>
+        <v>3.510364611669859</v>
       </c>
       <c r="D61" s="3" t="n">
-        <v>1.802093065959636</v>
+        <v>0.9730958696475938</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>3.510364611669859</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>1.578347585639134</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2015</v>
+        <v>2007</v>
       </c>
       <c r="B62" s="3" t="n">
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>1.736563670597928</v>
+        <v>3.503081988613427</v>
       </c>
       <c r="D62" s="3" t="n">
-        <v>1.736563670597928</v>
+        <v>0.9663482572553594</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>3.503081988613427</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>1.574182770292213</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2016</v>
+        <v>2008</v>
       </c>
       <c r="B63" s="3" t="n">
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>1.701458023418519</v>
+        <v>3.511977262947724</v>
       </c>
       <c r="D63" s="3" t="n">
-        <v>1.701458023418519</v>
+        <v>0.9679468457943928</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>3.511977262947724</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>1.579315616441613</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2017</v>
+        <v>2009</v>
       </c>
       <c r="B64" s="3" t="n">
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>1.706485331284896</v>
+        <v>3.659966834432548</v>
       </c>
       <c r="D64" s="3" t="n">
-        <v>1.706485331284896</v>
+        <v>0.9987989911525682</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>3.659966834432548</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>1.663656400667903</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2018</v>
+        <v>2010</v>
       </c>
       <c r="B65" s="3" t="n">
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>1.706468461382766</v>
+        <v>3.895029220883218</v>
       </c>
       <c r="D65" s="3" t="n">
-        <v>1.706468461382766</v>
+        <v>1.08707102952913</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>3.895029220883218</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>1.797973168277564</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2019</v>
+        <v>2011</v>
       </c>
       <c r="B66" s="3" t="n">
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>1.66293607450498</v>
+        <v>3.928708145482845</v>
       </c>
       <c r="D66" s="3" t="n">
-        <v>1.66293607450498</v>
+        <v>1.098462244663759</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>3.928708145482845</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>1.817336623051065</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2020</v>
+        <v>2012</v>
       </c>
       <c r="B67" s="3" t="n">
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>1.621662951538046</v>
+        <v>3.873060516572282</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>1.621662951538046</v>
+        <v>1.081787922016167</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>3.873060516572282</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1.785629013363977</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2021</v>
+        <v>2013</v>
       </c>
       <c r="B68" s="3" t="n">
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>1.812342349157434</v>
+        <v>3.969828417593377</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>1.812342349157434</v>
+        <v>1.124937779990045</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>3.969828417593377</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>1.840945271335736</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2022</v>
+        <v>2014</v>
       </c>
       <c r="B69" s="3" t="n">
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>1.921766663021468</v>
+        <v>3.902019605704997</v>
       </c>
       <c r="D69" s="3" t="n">
-        <v>1.921766663021468</v>
+        <v>1.105553487427663</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>3.902019605704997</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>1.802093065959636</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2023</v>
+        <v>2015</v>
       </c>
       <c r="B70" s="3" t="n">
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>1.894343014848968</v>
+        <v>3.78722769984821</v>
       </c>
       <c r="D70" s="3" t="n">
-        <v>1.894343014848968</v>
+        <v>1.054461857272374</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>3.78722769984821</v>
+      </c>
+      <c r="F70" s="3" t="n">
+        <v>1.736563670597928</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
+        <v>2016</v>
+      </c>
+      <c r="B71" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>3.725889523233838</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>1.030033760112109</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>3.725889523233838</v>
+      </c>
+      <c r="F71" s="3" t="n">
+        <v>1.701458023418519</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2017</v>
+      </c>
+      <c r="B72" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>3.734751306295955</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>1.041946104133642</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>3.734751306295955</v>
+      </c>
+      <c r="F72" s="3" t="n">
+        <v>1.706485331284896</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2018</v>
+      </c>
+      <c r="B73" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>3.734580425189309</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>1.060762070971495</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>3.734580425189309</v>
+      </c>
+      <c r="F73" s="3" t="n">
+        <v>1.706468461382766</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2019</v>
+      </c>
+      <c r="B74" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>3.658362876321421</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>1.038245565023048</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>3.658362876321421</v>
+      </c>
+      <c r="F74" s="3" t="n">
+        <v>1.66293607450498</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="B75" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>3.586289829238468</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0.9859418669647848</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>3.586289829238468</v>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>1.621662951538046</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2021</v>
+      </c>
+      <c r="B76" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C76" s="3" t="n">
+        <v>3.919731095385827</v>
+      </c>
+      <c r="D76" s="3" t="n">
+        <v>1.107399621064653</v>
+      </c>
+      <c r="E76" s="3" t="n">
+        <v>3.919731095385827</v>
+      </c>
+      <c r="F76" s="3" t="n">
+        <v>1.812342349157434</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2022</v>
+      </c>
+      <c r="B77" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>4.111381737640265</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>1.19721527510581</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>4.111381737640265</v>
+      </c>
+      <c r="F77" s="3" t="n">
+        <v>1.921766663021468</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2023</v>
+      </c>
+      <c r="B78" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>4.063187186315991</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>1.179548563611491</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>4.063187186315991</v>
+      </c>
+      <c r="F78" s="3" t="n">
+        <v>1.894343014848968</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
         <v>2024</v>
       </c>
-      <c r="B71" s="3" t="n">
-        <v/>
-      </c>
-      <c r="C71" s="3" t="n">
-        <v>1.830697867828891</v>
-      </c>
-      <c r="D71" s="3" t="n">
+      <c r="B79" s="3" t="n">
+        <v/>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>3.951851809800826</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>1.147145315529222</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>3.951851809800826</v>
+      </c>
+      <c r="F79" s="3" t="n">
         <v>1.830697867828891</v>
       </c>
     </row>
@@ -1477,10 +2073,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B89"/>
+  <dimension ref="A1:B104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1540,7 +2136,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>H.1</t>
+          <t>5.7 (rate, in-text); H.1 (S*, V* components)</t>
         </is>
       </c>
     </row>
@@ -1612,7 +2208,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>L03</t>
+          <t>L01</t>
         </is>
       </c>
     </row>
@@ -1624,7 +2220,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>P04</t>
+          <t>P02</t>
         </is>
       </c>
     </row>
@@ -1685,48 +2281,56 @@
       </c>
       <c r="B18" t="inlineStr"/>
     </row>
-    <row r="19"/>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>S506-EXT-MARX</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>BEA GDP-by-Industry + SIC partition A (I-O uplift kIO held)</t>
+        </is>
+      </c>
+    </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>S506-EXT-OLD-DEPRECATED</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>pre-review S512 level-splice hybrid</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t># S506 — Rate of Exploitation (e = S*/V*)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
+          <t># S506 — Rate of Exploitation (e = S*/V*)</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>**Source Table**: Appendix H.1</t>
-        </is>
-      </c>
+      <c r="B24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>**Units**: ratio</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
@@ -1734,7 +2338,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+          <t>**Source Table**: Appendix H.1</t>
         </is>
       </c>
     </row>
@@ -1742,7 +2346,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Units**: ratio</t>
         </is>
       </c>
     </row>
@@ -1750,19 +2354,23 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr"/>
-      <c r="B29" t="inlineStr"/>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>**Content Type**: time_series</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>**Status**: book_period_validated</t>
         </is>
       </c>
     </row>
@@ -1774,7 +2382,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>## Definition</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1786,7 +2394,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Rate of Exploitation: e = S*/V*. The book's central Marxian magnitude. Identity-checked against S505/S504 ratio.</t>
+          <t>## Definition</t>
         </is>
       </c>
     </row>
@@ -1798,7 +2406,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Rate of Exploitation: e = S*/V*. The book's central Marxian magnitude. Identity-checked against S505/S504 ratio.</t>
         </is>
       </c>
     </row>
@@ -1810,7 +2418,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>## Subseries</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1822,23 +2430,19 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>| Subseries | Source | Period | Units |</t>
+          <t>## Subseries</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>|---|---|---|---|</t>
-        </is>
-      </c>
+      <c r="B41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
       <c r="B42" t="inlineStr">
         <is>
-          <t>| `S506-A` | S&amp;T 1994 | 1948-1989 | ratio |</t>
+          <t>| Subseries | Source | Period | Units |</t>
         </is>
       </c>
     </row>
@@ -1846,7 +2450,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>| `S506-EXT` | BLS CES + BEA NIPA | 1990-2024 | ratio |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
@@ -1854,19 +2458,23 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>| `S506-COMBINED` |  | 1948-2024 | ratio |</t>
+          <t>| `S506-A` | S&amp;T 1994 | 1948-1989 | ratio |</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr"/>
-      <c r="B45" t="inlineStr"/>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>| `S506-EXT` | BLS CES + BEA NIPA | 1990-2024 | ratio |</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>| `S506-COMBINED` |  | 1948-2024 | ratio |</t>
         </is>
       </c>
     </row>
@@ -1878,7 +2486,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>## Construction</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1890,7 +2498,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>### S506-A (book period, 1948-1989)</t>
+          <t>## Construction</t>
         </is>
       </c>
     </row>
@@ -1902,35 +2510,35 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
+          <t>### S506-A (book period, 1948-1989)</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2. Extract column `S_star_V_star` (and the `year` index).</t>
-        </is>
-      </c>
+      <c r="B53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
+          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
-      <c r="B55" t="inlineStr"/>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2. Extract column `S_star_V_star` (and the `year` index).</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
+          <t>3. No further transformation — this is the canonical published value.</t>
         </is>
       </c>
     </row>
@@ -1942,7 +2550,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
         </is>
       </c>
     </row>
@@ -1954,7 +2562,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -1966,7 +2574,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>1948=1.70, 1958=2.01, 1967=2.10, 1972=1.99, 1977=2.10, 1989=2.44</t>
+          <t>## Reference Values (Validation Benchmarks)</t>
         </is>
       </c>
     </row>
@@ -1978,7 +2586,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tolerance class: `rate_series` (rel 0.001 / abs 0.01).</t>
+          <t>1948=1.70, 1958=2.01, 1967=2.10, 1972=1.99, 1977=2.10, 1989=2.44</t>
         </is>
       </c>
     </row>
@@ -1990,7 +2598,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Validator: `code/V03_validators/V03_S506_exploitation_rate.py` writes to `data/intermediate/validation/S506.json`.</t>
+          <t>Tolerance class: `rate_series` (rel 0.001 / abs 0.01).</t>
         </is>
       </c>
     </row>
@@ -2002,7 +2610,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Validator: `code/V03_validators/V03_S506_exploitation_rate.py` writes to `data/intermediate/validation/S506.json`.</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2622,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>## Provenance Chain</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -2026,23 +2634,19 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>```</t>
+          <t>## Provenance Chain</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
-        </is>
-      </c>
+      <c r="B73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S506_exploitation_rate.py</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -2050,7 +2654,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S506.csv</t>
+          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2662,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S506_exploitation_rate.py</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S506_exploitation_rate.py</t>
         </is>
       </c>
     </row>
@@ -2066,7 +2670,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S506.csv</t>
+          <t xml:space="preserve">       └── data/intermediate/S506.csv</t>
         </is>
       </c>
     </row>
@@ -2074,7 +2678,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S506_exploitation_rate.py</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S506_exploitation_rate.py</t>
         </is>
       </c>
     </row>
@@ -2082,19 +2686,23 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                 └── data/final/S506.csv</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr"/>
-      <c r="B80" t="inlineStr"/>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S506_exploitation_rate.py</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -2106,7 +2714,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>## Citations</t>
+          <t>---</t>
         </is>
       </c>
     </row>
@@ -2118,7 +2726,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
+          <t>## Citations</t>
         </is>
       </c>
     </row>
@@ -2130,7 +2738,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>---</t>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
         </is>
       </c>
     </row>
@@ -2142,7 +2750,115 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr"/>
+      <c r="B90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr"/>
+      <c r="B91" t="inlineStr">
+        <is>
           <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr"/>
+      <c r="B92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr"/>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr"/>
+      <c r="B94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr"/>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>**Extension REBUILT** (headline ROE fix for Prof. Tonak; P1_FORENSIC_REPORT.md + WP-A_REPORT.md).</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr"/>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>As-built subseries now: S506-A (book, unchanged) | S506-EXT = consistent BEA operating-surplus</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr"/>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>rate (VA_partA-comp)/comp, real SIC 1990-97 + BEA va_components 1998-2024, DISTINCT MEASURE,</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr"/>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>break flag DIV-A10 | S506-EXT-MARX = faithful-concept reconstruction (kIO=1.5714 held, DIV-A10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr"/>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>| S506-EXT-OLD-DEPRECATED = frozen pre-review 1.27 splice-hybrid (retained) | S506-COMBINED =</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>book + EXT-MARX with methodological-break annotation. Key values: EXT 1997=0.8021/1998=0.7891/</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr"/>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>2024=1.1471; MARX 1990=2.4673/1998=2.9707/2024=3.9519. The pre-review 2.44-&gt;1.27 cliff was</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr"/>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>~100% method (waterfall closes); it is gone. Subseries table above is superseded by this list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr"/>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>V03: PASS 6/6 book benchmarks + identity. Registry patches queued (WP-A_REGISTRY_PATCHES.json).</t>
         </is>
       </c>
     </row>
@@ -2309,12 +3025,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>e = S*/V*. The rate of exploitation measures how much surplus value is extracted per unit of variable capital. Under the approximation ec_u/ec_p ≈ 1, this simplifies to e = (GFP/W)(1/(V*/W)) - 1. For extension: e = 1.238/(V*/W) - 1, using the empirical constant derived from book-period GFP/W stability.</t>
+          <t>e = S*/V* = (VA* - V*)/V*. The rate of exploitation measures surplus value per unit of productive variable capital. WP-A 2026-07-01 REBUILD: the pre-review extension formula e = 1.238/(V*/W) - 1 (a constant-GFP/W shortcut) is RETIRED. As-built extension: (a) S506-EXT PRIMARY = consistent BEA operating-surplus rate (VA_partA - comp_partA)/comp_partA (a DISTINCT measure from the book Marxian e, with a methodological break at the 1989/1990 seam); (b) S506-EXT-MARX = closest book-faithful reconstruction holding the book-terminal I-O uplift kIO=1.5714 (the non-constructible Shaikh-Tonak final-demand reallocation; DIV-A10) with de-spliced V*/W. The book Marxian e (2.44) is NOT recoverable from BEA value-added aggregates: book VA*_1989=4149.75 vs BEA partition-A industry VA_1989=2776.8 (factor 1.571x lives in the I-O structure). See P1_FORENSIC_REPORT.md.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; Knowledge_Base/equations/page_340_equations.txt</t>
+          <t>ST_1994, Ch5; P1_FORENSIC_REPORT.md (WP-A rebuild)</t>
         </is>
       </c>
     </row>
@@ -2326,7 +3042,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Book benchmarks from Table 5.7: 1948=1.70, 1958=1.83, 1967=2.10, 1977=2.10, 1989=2.44. The rising trend reflects the secular decline in productive labor's share of total employment and compensation.</t>
+          <t>Book benchmarks from Table 5.7: 1948=1.70, 1958=2.01, 1967=2.10, 1977=2.10, 1989=2.44. (1958 corrected from a single-cell transcription error 1.83 -&gt; 2.01 on 2026-07-01; 2.01 confirmed by KB v2 _combined/H.1.csv S*/V* row 1957=1.88/1958=2.01/1959=1.99, Table 5.7 T506A, chopped/S506.csv, and registry reference_values which was already 2.01 — see P1_FORENSIC_REPORT §5.) The rising trend reflects the secular decline in productive labor's share of total employment and compensation.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -2360,12 +3076,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>The extension formula e = 1.238/(V*/W) - 1 derives from the observation that GFP/W ≈ 1.238 is approximately constant over the book period. Since e = S*/V* = (GFP - V*)/V* = (GFP/W)/(V*/W) - 1, and GFP/W is stable, the exploitation rate is driven primarily by changes in the productive wage share V*/W.</t>
+          <t>RETIRED (WP-A 2026-07-01). The pre-review shortcut e = 1.238/(V*/W) - 1 assumed a constant GFP/W ~ 1.238; the as-built pipeline never implemented it (it computed the S505-EXT/S504-EXT identity, then a splice-hybrid that manufactured the spurious 1.27@1998). Replaced by two honest, real-BEA arms: S506-EXT (consistent BEA operating-surplus rate, distinct measure) and S506-EXT-MARX (book-faithful reconstruction with held I-O uplift kIO=1.5714, DIV-A10). The productive-wage share V*/W (S512) is de-spliced (DIV-A11).</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>ST_1994, Ch5; DPR T506_DPR.md</t>
+          <t>P1_FORENSIC_REPORT.md; WP-A_REPORT.md</t>
         </is>
       </c>
     </row>
@@ -2460,7 +3176,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Rate of exploitation e = S*/V*, rising from 1.70 (1948) to 2.44 (1989). Extended via e = 1.238/(V*/W) - 1. Mohun comparison shows classification sensitivity (~2.3-2.5 vs ST's 2.6-2.7). [internal-decision-record]: VA*/W constant assumption partially resolved; 1990-1997 values interpolated ([internal-decision-record]).</t>
+          <t>Rate of exploitation e = S*/V*, rising from 1.70 (1948) to 2.44 (1989) in the book period. WP-A 2026-07-01 rebuilt the extension (P1_FORENSIC_REPORT): the pre-review 2.44-&gt;1.27 'drop' was a splice artifact (~100% method). As-built: S506-EXT = consistent BEA operating-surplus rate (0.73-&gt;0.80-&gt;1.15, a distinct measure with a 1989/1990 methodological break); S506-EXT-MARX = closest book-faithful reconstruction (~2.5-&gt;3.9, holds I-O uplift kIO=1.5714, DIV-A10) used for S506-COMBINED so the spurious drop is removed; the old 1.27 hybrid is retained frozen as S506-EXT-OLD-DEPRECATED. V*/W (S512) de-spliced with real SIC 1990-97 fill.</t>
         </is>
       </c>
     </row>
@@ -2476,7 +3192,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>GFP/W ≈ 1.238 constancy assumption may weaken post-1989</t>
+          <t>The book Marxian e is NOT reconstructible from BEA VA aggregates: the numerator GFP*/VA* is a Shaikh-Tonak I-O final-demand transform (kIO~1.571x at the 1989 seam) not present in any industry-VA sum; the extension holds it as a registered divergence (DIV-A10)</t>
         </is>
       </c>
     </row>
@@ -2484,7 +3200,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Classification-sensitive: Mohun's broader productive sector yields lower e</t>
+          <t>Classification-sensitive: Mohun's broader productive sector yields different e (see XS1403 Mohun variant)</t>
         </is>
       </c>
     </row>
@@ -2492,7 +3208,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Extension validity depends on S512 quality</t>
+          <t>S506-EXT-MARX carries residual seam texture at 1997/98 from the real SIC-&gt;NAICS vintage break (DIV-010) and the V*/W 0.36-&gt;0.27 break (documented, not spliced away)</t>
         </is>
       </c>
     </row>
@@ -2500,7 +3216,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>[internal-decision-record]: VA*/W constant carries small systematic error for 1990-1997 (interpolated per [internal-decision-record]) and post-1997 extension period</t>
+          <t>Extension validity depends on S512 (V*/W) quality</t>
         </is>
       </c>
     </row>
@@ -2587,14 +3303,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="4" max="4"/>
+    <col width="61" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2650,7 +3366,11 @@
           <t>derive</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>BEA_GDPbyIndustry_va_components, BEA_SIC_partitionA</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>S506-EXT</t>
@@ -2658,7 +3378,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>e = 1.238/(V*/W) - 1</t>
+          <t>e_bea = (VA_partA - comp_partA)/comp_partA</t>
         </is>
       </c>
     </row>
@@ -2668,209 +3388,263 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>derive</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>BEA_GDPbyIndustry_va_components, BEA_SIC_partitionA, BEA_NIPA_6_2D, BEA_NIPA_T20100</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>S506-EXT-MARX</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>e_marx = (kIO*VA_partA*(1-dp_ratio))/(s512_raw*W_total) - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>load</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>S506-EXT-OLD-DEPRECATED</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>splice</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>S506-A, S506-EXT</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S506-A, S506-EXT-MARX</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
         <is>
           <t>S506-COMBINED</t>
         </is>
       </c>
-      <c r="E4" t="n">
+      <c r="E6" t="n">
         <v>1989</v>
       </c>
     </row>
-    <row r="5"/>
-    <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+    <row r="7"/>
+    <row r="8">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B6" s="4" t="inlineStr"/>
-      <c r="C6" s="4" t="n"/>
-      <c r="D6" s="4" t="n"/>
-      <c r="E6" s="4" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>splice_year</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>1989</t>
-        </is>
-      </c>
+      <c r="B8" s="4" t="inlineStr"/>
+      <c r="C8" s="4" t="n"/>
+      <c r="D8" s="4" t="n"/>
+      <c r="E8" s="4" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>derive</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>output_subseries</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S506-EXT</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>combined_subseries</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S506-COMBINED</t>
+          <t>derive (two-arm rebuild; no level-splice; methodological break annotated at 1989/1990 - DIV-028)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>output_subseries</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.7 (rate of surplus value e = S*/V*); identity from Appendix H.1 series", "shaikh_appendix_ref": "Table 5.7 (rate of surplus value, 1948-1989); Appendix H.1 (S_star, V_star); Figure 5.6", "extension_source": "Derived ratio: e = S505 / S504. Inherits sources from S505 and S504 (which in turn depend on BLS CES + BEA NIPA).", "extension_url": "n/a (derived from S505 and S504)", "conceptual_continuity": "Rate of exploitation e = S*/V* is the Marxian ratio of surplus value to variable capital -- the rate at which capital extracts value from productive labor. It is a pure ratio of two derived/aggregate series, and per the Anu Extension Standard must be recomputed from extended components, NOT growth-rate spliced. Conceptual continuity holds as long as the numerator and denominator are extended with their Marxian definitions intact.", "vintage_note": "Inherits vintage divergences from S505 and S504. As a ratio, dimensionless, so unit-vintage issues cancel.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
+          <t>S506-EXT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>depends_on</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>["S512"]</t>
-        </is>
-      </c>
-    </row>
-    <row r="14"/>
+          <t>S506-COMBINED</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.7 (rate of surplus value e = S*/V*); identity from Appendix H.1 series", "shaikh_appendix_ref": "Table 5.7 (rate of surplus value, 1948-1989); Appendix H.1 (S_star, V_star); Figure 5.6", "extension_source": "Derived ratio: e = S505 / S504. Inherits sources from S505 and S504 (which in turn depend on BLS CES + BEA NIPA).", "extension_url": "n/a (derived from S505 and S504)", "conceptual_continuity": "Rate of exploitation e = S*/V* is the Marxian ratio of surplus value to variable capital -- the rate at which capital extracts value from productive labor. It is a pure ratio of two derived/aggregate series, and per the Anu Extension Standard must be recomputed from extended components, NOT growth-rate spliced. Conceptual continuity holds as long as the numerator and denominator are extended with their Marxian definitions intact.", "vintage_note": "Inherits vintage divergences from S505 and S504. As a ratio, dimensionless, so unit-vintage issues cancel.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
+        </is>
+      </c>
+    </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>reference_values</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>{"1948": 1.7, "1958": 2.01, "1967": 2.1, "1972": 1.99, "1977": 2.1, "1989": 2.44}</t>
-        </is>
-      </c>
-    </row>
+          <t>depends_on</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>["data/source/bea_sic/GDPbyInd_partitionA_SIC_1987_1997.csv", "gdp_by_industry_va_components.csv", "nipa_6_2D_compensation_by_industry.csv", "nipa_T20100_compensation_1929_2025.csv"]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>expected_range</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>[1.0, 5.0]</t>
-        </is>
-      </c>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>reference_values</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>{"1948": 1.7, "1958": 2.01, "1967": 2.1, "1972": 1.99, "1977": 2.1, "1989": 2.44}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>[1.0, 5.0]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>rate_series</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tolerance_abs</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>rate_series</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
+          <t>tolerance_rel</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0.001</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>tolerance_abs</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>extension_year_range</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>extension_reference_values</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>{"S506-EXT": {"1997": 0.8021, "1998": 0.7891, "2024": 1.1471}, "S506-EXT-OLD-DEPRECATED": {"1998": 1.27}}</t>
         </is>
       </c>
     </row>

--- a/extenbooks/S506.xlsx
+++ b/extenbooks/S506.xlsx
@@ -447,7 +447,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F79"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="41" customWidth="1" min="1" max="1"/>
@@ -455,7 +455,8 @@
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="62" customWidth="1" min="5" max="5"/>
-    <col width="50" customWidth="1" min="6" max="6"/>
+    <col width="62" customWidth="1" min="6" max="6"/>
+    <col width="50" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,6 +487,11 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>BEA benchmark I-O (1992 SIC + 1997-2017 NAICS) + annual 71-order SUTs; native 1992 level anchor + NAICS annual trend (WP-B1/B2/C splice), units=ratio</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
           <t>pre-review S512 level-splice hybrid, units=ratio</t>
         </is>
       </c>
@@ -517,6 +523,11 @@
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>S506-EXT-MARX-KIO</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
         <is>
           <t>S506-EXT-OLD-DEPRECATED</t>
         </is>
@@ -541,6 +552,9 @@
       <c r="F3" s="3" t="n">
         <v/>
       </c>
+      <c r="G3" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -561,6 +575,9 @@
       <c r="F4" s="3" t="n">
         <v/>
       </c>
+      <c r="G4" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -581,6 +598,9 @@
       <c r="F5" s="3" t="n">
         <v/>
       </c>
+      <c r="G5" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -601,6 +621,9 @@
       <c r="F6" s="3" t="n">
         <v/>
       </c>
+      <c r="G6" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -621,6 +644,9 @@
       <c r="F7" s="3" t="n">
         <v/>
       </c>
+      <c r="G7" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -641,6 +667,9 @@
       <c r="F8" s="3" t="n">
         <v/>
       </c>
+      <c r="G8" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -661,6 +690,9 @@
       <c r="F9" s="3" t="n">
         <v/>
       </c>
+      <c r="G9" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -681,6 +713,9 @@
       <c r="F10" s="3" t="n">
         <v/>
       </c>
+      <c r="G10" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -701,6 +736,9 @@
       <c r="F11" s="3" t="n">
         <v/>
       </c>
+      <c r="G11" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -721,6 +759,9 @@
       <c r="F12" s="3" t="n">
         <v/>
       </c>
+      <c r="G12" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -741,6 +782,9 @@
       <c r="F13" s="3" t="n">
         <v/>
       </c>
+      <c r="G13" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -761,6 +805,9 @@
       <c r="F14" s="3" t="n">
         <v/>
       </c>
+      <c r="G14" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -781,6 +828,9 @@
       <c r="F15" s="3" t="n">
         <v/>
       </c>
+      <c r="G15" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -801,6 +851,9 @@
       <c r="F16" s="3" t="n">
         <v/>
       </c>
+      <c r="G16" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -821,6 +874,9 @@
       <c r="F17" s="3" t="n">
         <v/>
       </c>
+      <c r="G17" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -841,6 +897,9 @@
       <c r="F18" s="3" t="n">
         <v/>
       </c>
+      <c r="G18" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -861,6 +920,9 @@
       <c r="F19" s="3" t="n">
         <v/>
       </c>
+      <c r="G19" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -881,6 +943,9 @@
       <c r="F20" s="3" t="n">
         <v/>
       </c>
+      <c r="G20" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -901,6 +966,9 @@
       <c r="F21" s="3" t="n">
         <v/>
       </c>
+      <c r="G21" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -921,6 +989,9 @@
       <c r="F22" s="3" t="n">
         <v/>
       </c>
+      <c r="G22" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -941,6 +1012,9 @@
       <c r="F23" s="3" t="n">
         <v/>
       </c>
+      <c r="G23" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -961,6 +1035,9 @@
       <c r="F24" s="3" t="n">
         <v/>
       </c>
+      <c r="G24" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -981,6 +1058,9 @@
       <c r="F25" s="3" t="n">
         <v/>
       </c>
+      <c r="G25" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -1001,6 +1081,9 @@
       <c r="F26" s="3" t="n">
         <v/>
       </c>
+      <c r="G26" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -1021,6 +1104,9 @@
       <c r="F27" s="3" t="n">
         <v/>
       </c>
+      <c r="G27" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -1041,6 +1127,9 @@
       <c r="F28" s="3" t="n">
         <v/>
       </c>
+      <c r="G28" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -1061,6 +1150,9 @@
       <c r="F29" s="3" t="n">
         <v/>
       </c>
+      <c r="G29" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -1081,6 +1173,9 @@
       <c r="F30" s="3" t="n">
         <v/>
       </c>
+      <c r="G30" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -1101,6 +1196,9 @@
       <c r="F31" s="3" t="n">
         <v/>
       </c>
+      <c r="G31" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -1121,6 +1219,9 @@
       <c r="F32" s="3" t="n">
         <v/>
       </c>
+      <c r="G32" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -1141,6 +1242,9 @@
       <c r="F33" s="3" t="n">
         <v/>
       </c>
+      <c r="G33" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -1161,6 +1265,9 @@
       <c r="F34" s="3" t="n">
         <v/>
       </c>
+      <c r="G34" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -1181,6 +1288,9 @@
       <c r="F35" s="3" t="n">
         <v/>
       </c>
+      <c r="G35" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -1201,6 +1311,9 @@
       <c r="F36" s="3" t="n">
         <v/>
       </c>
+      <c r="G36" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -1221,6 +1334,9 @@
       <c r="F37" s="3" t="n">
         <v/>
       </c>
+      <c r="G37" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -1241,6 +1357,9 @@
       <c r="F38" s="3" t="n">
         <v/>
       </c>
+      <c r="G38" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -1261,6 +1380,9 @@
       <c r="F39" s="3" t="n">
         <v/>
       </c>
+      <c r="G39" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -1281,6 +1403,9 @@
       <c r="F40" s="3" t="n">
         <v/>
       </c>
+      <c r="G40" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -1301,6 +1426,9 @@
       <c r="F41" s="3" t="n">
         <v/>
       </c>
+      <c r="G41" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -1321,6 +1449,9 @@
       <c r="F42" s="3" t="n">
         <v/>
       </c>
+      <c r="G42" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -1341,6 +1472,9 @@
       <c r="F43" s="3" t="n">
         <v/>
       </c>
+      <c r="G43" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -1361,6 +1495,9 @@
       <c r="F44" s="3" t="n">
         <v/>
       </c>
+      <c r="G44" s="3" t="n">
+        <v/>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -1370,7 +1507,7 @@
         <v/>
       </c>
       <c r="C45" s="3" t="n">
-        <v>2.467315213499074</v>
+        <v>2.433524941032656</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>0.7159641560036654</v>
@@ -1379,6 +1516,9 @@
         <v>2.467315213499074</v>
       </c>
       <c r="F45" s="3" t="n">
+        <v>2.433524941032656</v>
+      </c>
+      <c r="G45" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1390,7 +1530,7 @@
         <v/>
       </c>
       <c r="C46" s="3" t="n">
-        <v>2.51833159492349</v>
+        <v>2.504194780186186</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>0.7095017617597911</v>
@@ -1399,6 +1539,9 @@
         <v>2.51833159492349</v>
       </c>
       <c r="F46" s="3" t="n">
+        <v>2.504194780186186</v>
+      </c>
+      <c r="G46" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1410,7 +1553,7 @@
         <v/>
       </c>
       <c r="C47" s="3" t="n">
-        <v>2.580312523206792</v>
+        <v>2.575951634255042</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>0.7104278671342835</v>
@@ -1419,6 +1562,9 @@
         <v>2.580312523206792</v>
       </c>
       <c r="F47" s="3" t="n">
+        <v>2.575951634255042</v>
+      </c>
+      <c r="G47" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1430,7 +1576,7 @@
         <v/>
       </c>
       <c r="C48" s="3" t="n">
-        <v>2.740840029977277</v>
+        <v>2.745329730616934</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>0.7262851098059526</v>
@@ -1439,6 +1585,9 @@
         <v>2.740840029977277</v>
       </c>
       <c r="F48" s="3" t="n">
+        <v>2.745329730616934</v>
+      </c>
+      <c r="G48" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1450,7 +1599,7 @@
         <v/>
       </c>
       <c r="C49" s="3" t="n">
-        <v>3.010901925958908</v>
+        <v>3.020054857705315</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>0.7593407911191818</v>
@@ -1459,6 +1608,9 @@
         <v>3.010901925958908</v>
       </c>
       <c r="F49" s="3" t="n">
+        <v>3.020054857705315</v>
+      </c>
+      <c r="G49" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1470,7 +1622,7 @@
         <v/>
       </c>
       <c r="C50" s="3" t="n">
-        <v>3.161125328931637</v>
+        <v>3.169032264461713</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>0.7651076185758044</v>
@@ -1479,6 +1631,9 @@
         <v>3.161125328931637</v>
       </c>
       <c r="F50" s="3" t="n">
+        <v>3.169032264461713</v>
+      </c>
+      <c r="G50" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1490,7 +1645,7 @@
         <v/>
       </c>
       <c r="C51" s="3" t="n">
-        <v>3.355580194486014</v>
+        <v>3.355264180077708</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>0.8021141813675748</v>
@@ -1499,6 +1654,9 @@
         <v>3.355580194486014</v>
       </c>
       <c r="F51" s="3" t="n">
+        <v>3.355264180077708</v>
+      </c>
+      <c r="G51" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1510,7 +1668,7 @@
         <v/>
       </c>
       <c r="C52" s="3" t="n">
-        <v>3.503306012029305</v>
+        <v>3.508137659667258</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>0.8021295418354709</v>
@@ -1519,6 +1677,9 @@
         <v>3.503306012029305</v>
       </c>
       <c r="F52" s="3" t="n">
+        <v>3.508137659667258</v>
+      </c>
+      <c r="G52" s="3" t="n">
         <v/>
       </c>
     </row>
@@ -1530,7 +1691,7 @@
         <v/>
       </c>
       <c r="C53" s="3" t="n">
-        <v>2.970693723369081</v>
+        <v>2.965857342668573</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0.7891049047666041</v>
@@ -1539,6 +1700,9 @@
         <v>2.970693723369081</v>
       </c>
       <c r="F53" s="3" t="n">
+        <v>2.965857342668573</v>
+      </c>
+      <c r="G53" s="3" t="n">
         <v>1.269989215720135</v>
       </c>
     </row>
@@ -1550,7 +1714,7 @@
         <v/>
       </c>
       <c r="C54" s="3" t="n">
-        <v>2.934462920074003</v>
+        <v>2.957963296492239</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>0.7764347622394002</v>
@@ -1559,6 +1723,9 @@
         <v>2.934462920074003</v>
       </c>
       <c r="F54" s="3" t="n">
+        <v>2.957963296492239</v>
+      </c>
+      <c r="G54" s="3" t="n">
         <v>1.248971860241347</v>
       </c>
     </row>
@@ -1570,7 +1737,7 @@
         <v/>
       </c>
       <c r="C55" s="3" t="n">
-        <v>2.909339725853235</v>
+        <v>2.936172941091812</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>0.7612719298245614</v>
@@ -1579,6 +1746,9 @@
         <v>2.909339725853235</v>
       </c>
       <c r="F55" s="3" t="n">
+        <v>2.936172941091812</v>
+      </c>
+      <c r="G55" s="3" t="n">
         <v>1.234673454504817</v>
       </c>
     </row>
@@ -1590,7 +1760,7 @@
         <v/>
       </c>
       <c r="C56" s="3" t="n">
-        <v>2.908468356161119</v>
+        <v>2.921118378403261</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>0.748118985126859</v>
@@ -1599,6 +1769,9 @@
         <v>2.908468356161119</v>
       </c>
       <c r="F56" s="3" t="n">
+        <v>2.921118378403261</v>
+      </c>
+      <c r="G56" s="3" t="n">
         <v>1.23411917806487</v>
       </c>
     </row>
@@ -1610,7 +1783,7 @@
         <v/>
       </c>
       <c r="C57" s="3" t="n">
-        <v>3.00986818445747</v>
+        <v>3.087916221600974</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>0.7698707735882457</v>
@@ -1619,6 +1792,9 @@
         <v>3.00986818445747</v>
       </c>
       <c r="F57" s="3" t="n">
+        <v>3.087916221600974</v>
+      </c>
+      <c r="G57" s="3" t="n">
         <v>1.292137725442533</v>
       </c>
     </row>
@@ -1630,7 +1806,7 @@
         <v/>
       </c>
       <c r="C58" s="3" t="n">
-        <v>3.196929936513684</v>
+        <v>3.275948143523135</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>0.8375435540069687</v>
@@ -1639,6 +1815,9 @@
         <v>3.196929936513684</v>
       </c>
       <c r="F58" s="3" t="n">
+        <v>3.275948143523135</v>
+      </c>
+      <c r="G58" s="3" t="n">
         <v>1.399126741490147</v>
       </c>
     </row>
@@ -1650,7 +1829,7 @@
         <v/>
       </c>
       <c r="C59" s="3" t="n">
-        <v>3.320905184104303</v>
+        <v>3.417380858373289</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>0.8922743922743922</v>
@@ -1659,6 +1838,9 @@
         <v>3.320905184104303</v>
       </c>
       <c r="F59" s="3" t="n">
+        <v>3.417380858373289</v>
+      </c>
+      <c r="G59" s="3" t="n">
         <v>1.469995766295596</v>
       </c>
     </row>
@@ -1670,7 +1852,7 @@
         <v/>
       </c>
       <c r="C60" s="3" t="n">
-        <v>3.436829782324695</v>
+        <v>3.531376239599145</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>0.9392333439591968</v>
@@ -1679,6 +1861,9 @@
         <v>3.436829782324695</v>
       </c>
       <c r="F60" s="3" t="n">
+        <v>3.531376239599145</v>
+      </c>
+      <c r="G60" s="3" t="n">
         <v>1.53626272995572</v>
       </c>
     </row>
@@ -1690,7 +1875,7 @@
         <v/>
       </c>
       <c r="C61" s="3" t="n">
-        <v>3.510364611669859</v>
+        <v>3.603033746280845</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>0.9730958696475938</v>
@@ -1699,6 +1884,9 @@
         <v>3.510364611669859</v>
       </c>
       <c r="F61" s="3" t="n">
+        <v>3.603033746280845</v>
+      </c>
+      <c r="G61" s="3" t="n">
         <v>1.578347585639134</v>
       </c>
     </row>
@@ -1710,7 +1898,7 @@
         <v/>
       </c>
       <c r="C62" s="3" t="n">
-        <v>3.503081988613427</v>
+        <v>3.610502741500276</v>
       </c>
       <c r="D62" s="3" t="n">
         <v>0.9663482572553594</v>
@@ -1719,6 +1907,9 @@
         <v>3.503081988613427</v>
       </c>
       <c r="F62" s="3" t="n">
+        <v>3.610502741500276</v>
+      </c>
+      <c r="G62" s="3" t="n">
         <v>1.574182770292213</v>
       </c>
     </row>
@@ -1730,7 +1921,7 @@
         <v/>
       </c>
       <c r="C63" s="3" t="n">
-        <v>3.511977262947724</v>
+        <v>3.627649809683938</v>
       </c>
       <c r="D63" s="3" t="n">
         <v>0.9679468457943928</v>
@@ -1739,6 +1930,9 @@
         <v>3.511977262947724</v>
       </c>
       <c r="F63" s="3" t="n">
+        <v>3.627649809683938</v>
+      </c>
+      <c r="G63" s="3" t="n">
         <v>1.579315616441613</v>
       </c>
     </row>
@@ -1750,7 +1944,7 @@
         <v/>
       </c>
       <c r="C64" s="3" t="n">
-        <v>3.659966834432548</v>
+        <v>3.743254733381078</v>
       </c>
       <c r="D64" s="3" t="n">
         <v>0.9987989911525682</v>
@@ -1759,6 +1953,9 @@
         <v>3.659966834432548</v>
       </c>
       <c r="F64" s="3" t="n">
+        <v>3.743254733381078</v>
+      </c>
+      <c r="G64" s="3" t="n">
         <v>1.663656400667903</v>
       </c>
     </row>
@@ -1770,7 +1967,7 @@
         <v/>
       </c>
       <c r="C65" s="3" t="n">
-        <v>3.895029220883218</v>
+        <v>4.110546856023007</v>
       </c>
       <c r="D65" s="3" t="n">
         <v>1.08707102952913</v>
@@ -1779,6 +1976,9 @@
         <v>3.895029220883218</v>
       </c>
       <c r="F65" s="3" t="n">
+        <v>4.110546856023007</v>
+      </c>
+      <c r="G65" s="3" t="n">
         <v>1.797973168277564</v>
       </c>
     </row>
@@ -1790,7 +1990,7 @@
         <v/>
       </c>
       <c r="C66" s="3" t="n">
-        <v>3.928708145482845</v>
+        <v>4.191501195001177</v>
       </c>
       <c r="D66" s="3" t="n">
         <v>1.098462244663759</v>
@@ -1799,6 +1999,9 @@
         <v>3.928708145482845</v>
       </c>
       <c r="F66" s="3" t="n">
+        <v>4.191501195001177</v>
+      </c>
+      <c r="G66" s="3" t="n">
         <v>1.817336623051065</v>
       </c>
     </row>
@@ -1810,7 +2013,7 @@
         <v/>
       </c>
       <c r="C67" s="3" t="n">
-        <v>3.873060516572282</v>
+        <v>4.186224855078584</v>
       </c>
       <c r="D67" s="3" t="n">
         <v>1.081787922016167</v>
@@ -1819,6 +2022,9 @@
         <v>3.873060516572282</v>
       </c>
       <c r="F67" s="3" t="n">
+        <v>4.186224855078584</v>
+      </c>
+      <c r="G67" s="3" t="n">
         <v>1.785629013363977</v>
       </c>
     </row>
@@ -1830,7 +2036,7 @@
         <v/>
       </c>
       <c r="C68" s="3" t="n">
-        <v>3.969828417593377</v>
+        <v>4.317991578968347</v>
       </c>
       <c r="D68" s="3" t="n">
         <v>1.124937779990045</v>
@@ -1839,6 +2045,9 @@
         <v>3.969828417593377</v>
       </c>
       <c r="F68" s="3" t="n">
+        <v>4.317991578968347</v>
+      </c>
+      <c r="G68" s="3" t="n">
         <v>1.840945271335736</v>
       </c>
     </row>
@@ -1850,7 +2059,7 @@
         <v/>
       </c>
       <c r="C69" s="3" t="n">
-        <v>3.902019605704997</v>
+        <v>4.285985842781519</v>
       </c>
       <c r="D69" s="3" t="n">
         <v>1.105553487427663</v>
@@ -1859,6 +2068,9 @@
         <v>3.902019605704997</v>
       </c>
       <c r="F69" s="3" t="n">
+        <v>4.285985842781519</v>
+      </c>
+      <c r="G69" s="3" t="n">
         <v>1.802093065959636</v>
       </c>
     </row>
@@ -1870,7 +2082,7 @@
         <v/>
       </c>
       <c r="C70" s="3" t="n">
-        <v>3.78722769984821</v>
+        <v>4.213687431629708</v>
       </c>
       <c r="D70" s="3" t="n">
         <v>1.054461857272374</v>
@@ -1879,6 +2091,9 @@
         <v>3.78722769984821</v>
       </c>
       <c r="F70" s="3" t="n">
+        <v>4.213687431629708</v>
+      </c>
+      <c r="G70" s="3" t="n">
         <v>1.736563670597928</v>
       </c>
     </row>
@@ -1890,7 +2105,7 @@
         <v/>
       </c>
       <c r="C71" s="3" t="n">
-        <v>3.725889523233838</v>
+        <v>4.193499965054668</v>
       </c>
       <c r="D71" s="3" t="n">
         <v>1.030033760112109</v>
@@ -1899,6 +2114,9 @@
         <v>3.725889523233838</v>
       </c>
       <c r="F71" s="3" t="n">
+        <v>4.193499965054668</v>
+      </c>
+      <c r="G71" s="3" t="n">
         <v>1.701458023418519</v>
       </c>
     </row>
@@ -1910,7 +2128,7 @@
         <v/>
       </c>
       <c r="C72" s="3" t="n">
-        <v>3.734751306295955</v>
+        <v>4.209565999032023</v>
       </c>
       <c r="D72" s="3" t="n">
         <v>1.041946104133642</v>
@@ -1919,6 +2137,9 @@
         <v>3.734751306295955</v>
       </c>
       <c r="F72" s="3" t="n">
+        <v>4.209565999032023</v>
+      </c>
+      <c r="G72" s="3" t="n">
         <v>1.706485331284896</v>
       </c>
     </row>
@@ -1930,7 +2151,7 @@
         <v/>
       </c>
       <c r="C73" s="3" t="n">
-        <v>3.734580425189309</v>
+        <v>4.200640447549623</v>
       </c>
       <c r="D73" s="3" t="n">
         <v>1.060762070971495</v>
@@ -1939,6 +2160,9 @@
         <v>3.734580425189309</v>
       </c>
       <c r="F73" s="3" t="n">
+        <v>4.200640447549623</v>
+      </c>
+      <c r="G73" s="3" t="n">
         <v>1.706468461382766</v>
       </c>
     </row>
@@ -1950,7 +2174,7 @@
         <v/>
       </c>
       <c r="C74" s="3" t="n">
-        <v>3.658362876321421</v>
+        <v>4.08935094364544</v>
       </c>
       <c r="D74" s="3" t="n">
         <v>1.038245565023048</v>
@@ -1959,6 +2183,9 @@
         <v>3.658362876321421</v>
       </c>
       <c r="F74" s="3" t="n">
+        <v>4.08935094364544</v>
+      </c>
+      <c r="G74" s="3" t="n">
         <v>1.66293607450498</v>
       </c>
     </row>
@@ -1970,7 +2197,7 @@
         <v/>
       </c>
       <c r="C75" s="3" t="n">
-        <v>3.586289829238468</v>
+        <v>4.046216371351194</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0.9859418669647848</v>
@@ -1979,6 +2206,9 @@
         <v>3.586289829238468</v>
       </c>
       <c r="F75" s="3" t="n">
+        <v>4.046216371351194</v>
+      </c>
+      <c r="G75" s="3" t="n">
         <v>1.621662951538046</v>
       </c>
     </row>
@@ -1990,7 +2220,7 @@
         <v/>
       </c>
       <c r="C76" s="3" t="n">
-        <v>3.919731095385827</v>
+        <v>4.507332187739665</v>
       </c>
       <c r="D76" s="3" t="n">
         <v>1.107399621064653</v>
@@ -1999,6 +2229,9 @@
         <v>3.919731095385827</v>
       </c>
       <c r="F76" s="3" t="n">
+        <v>4.507332187739665</v>
+      </c>
+      <c r="G76" s="3" t="n">
         <v>1.812342349157434</v>
       </c>
     </row>
@@ -2010,7 +2243,7 @@
         <v/>
       </c>
       <c r="C77" s="3" t="n">
-        <v>4.111381737640265</v>
+        <v>4.709187493560785</v>
       </c>
       <c r="D77" s="3" t="n">
         <v>1.19721527510581</v>
@@ -2019,6 +2252,9 @@
         <v>4.111381737640265</v>
       </c>
       <c r="F77" s="3" t="n">
+        <v>4.709187493560785</v>
+      </c>
+      <c r="G77" s="3" t="n">
         <v>1.921766663021468</v>
       </c>
     </row>
@@ -2030,7 +2266,7 @@
         <v/>
       </c>
       <c r="C78" s="3" t="n">
-        <v>4.063187186315991</v>
+        <v>4.588659707906949</v>
       </c>
       <c r="D78" s="3" t="n">
         <v>1.179548563611491</v>
@@ -2039,6 +2275,9 @@
         <v>4.063187186315991</v>
       </c>
       <c r="F78" s="3" t="n">
+        <v>4.588659707906949</v>
+      </c>
+      <c r="G78" s="3" t="n">
         <v>1.894343014848968</v>
       </c>
     </row>
@@ -2050,7 +2289,7 @@
         <v/>
       </c>
       <c r="C79" s="3" t="n">
-        <v>3.951851809800826</v>
+        <v>4.455055511251512</v>
       </c>
       <c r="D79" s="3" t="n">
         <v>1.147145315529222</v>
@@ -2059,6 +2298,9 @@
         <v>3.951851809800826</v>
       </c>
       <c r="F79" s="3" t="n">
+        <v>4.455055511251512</v>
+      </c>
+      <c r="G79" s="3" t="n">
         <v>1.830697867828891</v>
       </c>
     </row>
@@ -2073,7 +2315,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B104"/>
+  <dimension ref="A1:B107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2184,7 +2426,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>book_period_validated</t>
+          <t>validated_book_and_extension</t>
         </is>
       </c>
     </row>
@@ -2305,40 +2547,44 @@
         </is>
       </c>
     </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>S506-EXT-MARX-KIO</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>BEA benchmark I-O (1992 SIC + 1997-2017 NAICS) + annual 71-order SUTs; native 1992 level anchor + NAICS annual trend (WP-B1/B2/C splice)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22"/>
+    <row r="23">
+      <c r="A23" t="inlineStr">
         <is>
           <t>DPR (markdown)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t># S506 — Rate of Exploitation (e = S*/V*)</t>
-        </is>
-      </c>
+      <c r="B23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
-      <c r="B24" t="inlineStr"/>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t># S506 — Rate of Exploitation (e = S*/V*)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr"/>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
-        </is>
-      </c>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>**Source Table**: Appendix H.1</t>
+          <t>**Chapter**: 5 — The Marxian Categories: Empirical Estimates</t>
         </is>
       </c>
     </row>
@@ -2346,7 +2592,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>**Units**: ratio</t>
+          <t>**Source Table**: Appendix H.1</t>
         </is>
       </c>
     </row>
@@ -2354,7 +2600,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
+          <t>**Units**: ratio</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2608,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>**Content Type**: time_series</t>
+          <t>**Period**: 1948-1989 (book period; extension via BEA NIPA + BLS CES when API access provisioned)</t>
         </is>
       </c>
     </row>
@@ -2370,87 +2616,87 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>**Status**: book_period_validated</t>
+          <t>**Content Type**: time_series</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr"/>
-      <c r="B31" t="inlineStr"/>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>**Status**: validated_book_and_extension</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr"/>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr"/>
-      <c r="B33" t="inlineStr"/>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr"/>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>## Definition</t>
-        </is>
-      </c>
+      <c r="B34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr"/>
-      <c r="B35" t="inlineStr"/>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>## Definition</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr"/>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Rate of Exploitation: e = S*/V*. The book's central Marxian magnitude. Identity-checked against S505/S504 ratio.</t>
-        </is>
-      </c>
+      <c r="B36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr"/>
-      <c r="B37" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Rate of Exploitation: e = S*/V*. The book's central Marxian magnitude. Identity-checked against S505/S504 ratio.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr"/>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr"/>
-      <c r="B39" t="inlineStr"/>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr"/>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>## Subseries</t>
-        </is>
-      </c>
+      <c r="B40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr"/>
-      <c r="B41" t="inlineStr"/>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>## Subseries</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr"/>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>| Subseries | Source | Period | Units |</t>
-        </is>
-      </c>
+      <c r="B42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>|---|---|---|---|</t>
+          <t>| Subseries | Source | Period | Units |</t>
         </is>
       </c>
     </row>
@@ -2458,7 +2704,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>| `S506-A` | S&amp;T 1994 | 1948-1989 | ratio |</t>
+          <t>|---|---|---|---|</t>
         </is>
       </c>
     </row>
@@ -2466,7 +2712,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>| `S506-EXT` | BLS CES + BEA NIPA | 1990-2024 | ratio |</t>
+          <t>| `S506-A` | S&amp;T 1994 | 1948-1989 | ratio |</t>
         </is>
       </c>
     </row>
@@ -2474,63 +2720,63 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>| `S506-COMBINED` |  | 1948-2024 | ratio |</t>
+          <t>| `S506-EXT` | BLS CES + BEA NIPA | 1990-2024 | ratio |</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr"/>
-      <c r="B47" t="inlineStr"/>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>| `S506-COMBINED` |  | 1948-2024 | ratio |</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr"/>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr"/>
-      <c r="B49" t="inlineStr"/>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr"/>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>## Construction</t>
-        </is>
-      </c>
+      <c r="B50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr"/>
-      <c r="B51" t="inlineStr"/>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>## Construction</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr"/>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>### S506-A (book period, 1948-1989)</t>
-        </is>
-      </c>
+      <c r="B52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr"/>
-      <c r="B53" t="inlineStr"/>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>### S506-A (book period, 1948-1989)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr"/>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
-        </is>
-      </c>
+      <c r="B54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2. Extract column `S_star_V_star` (and the `year` index).</t>
+          <t>1. Read `data/source/book_tables/book_tableH1_1948_1989.csv`.</t>
         </is>
       </c>
     </row>
@@ -2538,123 +2784,123 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>3. No further transformation — this is the canonical published value.</t>
+          <t>2. Extract column `S_star_V_star` (and the `year` index).</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr"/>
-      <c r="B57" t="inlineStr"/>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>3. No further transformation — this is the canonical published value.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr"/>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
-        </is>
-      </c>
+      <c r="B58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr"/>
-      <c r="B59" t="inlineStr"/>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Validator includes an identity check that verifies the algebraic relation against other already-built series in this chapter.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr"/>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr"/>
-      <c r="B61" t="inlineStr"/>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr"/>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>## Reference Values (Validation Benchmarks)</t>
-        </is>
-      </c>
+      <c r="B62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr"/>
-      <c r="B63" t="inlineStr"/>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>## Reference Values (Validation Benchmarks)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr"/>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>1948=1.70, 1958=2.01, 1967=2.10, 1972=1.99, 1977=2.10, 1989=2.44</t>
-        </is>
-      </c>
+      <c r="B64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr"/>
-      <c r="B65" t="inlineStr"/>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1948=1.70, 1958=2.01, 1967=2.10, 1972=1.99, 1977=2.10, 1989=2.44</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr"/>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Tolerance class: `rate_series` (rel 0.001 / abs 0.01).</t>
-        </is>
-      </c>
+      <c r="B66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr"/>
-      <c r="B67" t="inlineStr"/>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Tolerance class: `rate_series` (rel 0.001 / abs 0.01).</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr"/>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Validator: `code/V03_validators/V03_S506_exploitation_rate.py` writes to `data/intermediate/validation/S506.json`.</t>
-        </is>
-      </c>
+      <c r="B68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr"/>
-      <c r="B69" t="inlineStr"/>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Validator: `code/V03_validators/V03_S506_exploitation_rate.py` writes to `data/intermediate/validation/S506.json`.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr"/>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr"/>
-      <c r="B71" t="inlineStr"/>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr"/>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>## Provenance Chain</t>
-        </is>
-      </c>
+      <c r="B72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr"/>
-      <c r="B73" t="inlineStr"/>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>## Provenance Chain</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr"/>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>```</t>
-        </is>
-      </c>
+      <c r="B74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
+          <t>```</t>
         </is>
       </c>
     </row>
@@ -2662,7 +2908,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t xml:space="preserve">  └── code/L01_loaders/L01_S506_exploitation_rate.py</t>
+          <t>data/source/book_tables/book_tableH1_1948_1989.csv</t>
         </is>
       </c>
     </row>
@@ -2670,7 +2916,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t xml:space="preserve">       └── data/intermediate/S506.csv</t>
+          <t xml:space="preserve">  └── code/L01_loaders/L01_S506_exploitation_rate.py</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2924,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t xml:space="preserve">            └── code/P02_processors/P02_S506_exploitation_rate.py</t>
+          <t xml:space="preserve">       └── data/intermediate/S506.csv</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2932,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t xml:space="preserve">                 └── data/final/S506.csv</t>
+          <t xml:space="preserve">            └── code/P02_processors/P02_S506_exploitation_rate.py</t>
         </is>
       </c>
     </row>
@@ -2694,7 +2940,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t xml:space="preserve">                      └── code/V03_validators/V03_S506_exploitation_rate.py</t>
+          <t xml:space="preserve">                 └── data/final/S506.csv</t>
         </is>
       </c>
     </row>
@@ -2702,99 +2948,99 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>```</t>
+          <t xml:space="preserve">                      └── code/V03_validators/V03_S506_exploitation_rate.py</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr"/>
-      <c r="B82" t="inlineStr"/>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>```</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr"/>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr"/>
-      <c r="B84" t="inlineStr"/>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr"/>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>## Citations</t>
-        </is>
-      </c>
+      <c r="B85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr"/>
-      <c r="B86" t="inlineStr"/>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>## Citations</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr"/>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
-        </is>
-      </c>
+      <c r="B87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr"/>
-      <c r="B88" t="inlineStr"/>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Shaikh, Anwar, and E. Ahmet Tonak. 1994. *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press. Appendix H (Annual Time Series), p. 324-327. Cross-check vs. Appendix E.2 (Revenue Accounts, p. 310).</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr"/>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr"/>
-      <c r="B90" t="inlineStr"/>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr"/>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
-        </is>
-      </c>
+      <c r="B91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr"/>
-      <c r="B92" t="inlineStr"/>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>*Generated by anu-ingestion (re-authored from scratch against the Anu Framework v10.0 standard).*</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr"/>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>---</t>
-        </is>
-      </c>
+      <c r="B93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr"/>
-      <c r="B94" t="inlineStr"/>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>---</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr"/>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
-        </is>
-      </c>
+      <c r="B95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>**Extension REBUILT** (headline ROE fix for Prof. Tonak; P1_FORENSIC_REPORT.md + WP-A_REPORT.md).</t>
+          <t>## WP-A REBUILD ADDENDUM (2026-07-01, comprehensive review)</t>
         </is>
       </c>
     </row>
@@ -2802,7 +3048,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>As-built subseries now: S506-A (book, unchanged) | S506-EXT = consistent BEA operating-surplus</t>
+          <t>**Extension REBUILT** (headline ROE fix for Prof. Tonak; P1_FORENSIC_REPORT.md + WP-A_REPORT.md).</t>
         </is>
       </c>
     </row>
@@ -2810,7 +3056,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>rate (VA_partA-comp)/comp, real SIC 1990-97 + BEA va_components 1998-2024, DISTINCT MEASURE,</t>
+          <t>As-built subseries now: S506-A (book, unchanged) | S506-EXT = consistent BEA operating-surplus</t>
         </is>
       </c>
     </row>
@@ -2818,7 +3064,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>break flag DIV-A10 | S506-EXT-MARX = faithful-concept reconstruction (kIO=1.5714 held, DIV-A10)</t>
+          <t>rate (VA_partA-comp)/comp, real SIC 1990-97 + BEA va_components 1998-2024, DISTINCT MEASURE,</t>
         </is>
       </c>
     </row>
@@ -2826,7 +3072,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>| S506-EXT-OLD-DEPRECATED = frozen pre-review 1.27 splice-hybrid (retained) | S506-COMBINED =</t>
+          <t>break flag DIV-A10 | S506-EXT-MARX = faithful-concept reconstruction (kIO=1.5714 held, DIV-A10)</t>
         </is>
       </c>
     </row>
@@ -2834,7 +3080,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>book + EXT-MARX with methodological-break annotation. Key values: EXT 1997=0.8021/1998=0.7891/</t>
+          <t>| S506-EXT-OLD-DEPRECATED = frozen pre-review 1.27 splice-hybrid (retained) | S506-COMBINED =</t>
         </is>
       </c>
     </row>
@@ -2842,7 +3088,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024=1.1471; MARX 1990=2.4673/1998=2.9707/2024=3.9519. The pre-review 2.44-&gt;1.27 cliff was</t>
+          <t>book + EXT-MARX with methodological-break annotation. Key values: EXT 1997=0.8021/1998=0.7891/</t>
         </is>
       </c>
     </row>
@@ -2850,7 +3096,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>~100% method (waterfall closes); it is gone. Subseries table above is superseded by this list.</t>
+          <t>2024=1.1471; MARX 1990=2.4673/1998=2.9707/2024=3.9519. The pre-review 2.44-&gt;1.27 cliff was</t>
         </is>
       </c>
     </row>
@@ -2858,7 +3104,27 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
+          <t>~100% method (waterfall closes); it is gone. Subseries table above is superseded by this list.</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr"/>
+      <c r="B105" t="inlineStr">
+        <is>
           <t>V03: PASS 6/6 book benchmarks + identity. Registry patches queued (WP-A_REGISTRY_PATCHES.json).</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr"/>
+      <c r="B106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr"/>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>&gt; Status upgraded book_period_validated -&gt; validated_book_and_extension on 2026-07-07 (Phase-0 truth baseline, T3): populated extension block + -EXT/-COMBINED subseries + book-arm V03 PASS; parity with the pre-existing validated_book_and_extension series. See registry field `status_adjudication_2026_07_07`.</t>
         </is>
       </c>
     </row>
@@ -3303,14 +3569,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="62" customWidth="1" min="2" max="2"/>
     <col width="62" customWidth="1" min="3" max="3"/>
     <col width="25" customWidth="1" min="4" max="4"/>
-    <col width="61" customWidth="1" min="5" max="5"/>
+    <col width="62" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3435,7 +3701,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>S506-A, S506-EXT-MARX</t>
+          <t>S506-A, S506-EXT-MARX-KIO</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -3447,151 +3713,164 @@
         <v>1989</v>
       </c>
     </row>
-    <row r="7"/>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>derive</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>data/source/kio_reconstruction/kio_final_1990_2024.csv, BEA_GDPbyIndustry_va_components, BEA_SIC_partitionA, BEA_NIPA_6_2D, BEA_NIPA_T20100</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>S506-EXT-MARX-KIO</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>e_marx_kio = (kIO(t)*VA_partA*(1-dp_ratio))/(s512_raw*W_total) - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>EXTENSION</t>
         </is>
       </c>
-      <c r="B8" s="4" t="inlineStr"/>
-      <c r="C8" s="4" t="n"/>
-      <c r="D8" s="4" t="n"/>
-      <c r="E8" s="4" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>api</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>BLS</t>
-        </is>
-      </c>
+      <c r="B9" s="4" t="inlineStr"/>
+      <c r="C9" s="4" t="n"/>
+      <c r="D9" s="4" t="n"/>
+      <c r="E9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>splice_year</t>
+          <t>api</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>BLS</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>splice_method</t>
+          <t>splice_year</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>derive (two-arm rebuild; no level-splice; methodological break annotated at 1989/1990 - DIV-028)</t>
+          <t>1989</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>output_subseries</t>
+          <t>splice_method</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S506-EXT</t>
+          <t>derive (two-arm rebuild; no level-splice; methodological break annotated at 1989/1990 - DIV-028)</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>combined_subseries</t>
+          <t>output_subseries</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>S506-COMBINED</t>
+          <t>S506-EXT</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>provenance</t>
+          <t>combined_subseries</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.7 (rate of surplus value e = S*/V*); identity from Appendix H.1 series", "shaikh_appendix_ref": "Table 5.7 (rate of surplus value, 1948-1989); Appendix H.1 (S_star, V_star); Figure 5.6", "extension_source": "Derived ratio: e = S505 / S504. Inherits sources from S505 and S504 (which in turn depend on BLS CES + BEA NIPA).", "extension_url": "n/a (derived from S505 and S504)", "conceptual_continuity": "Rate of exploitation e = S*/V* is the Marxian ratio of surplus value to variable capital -- the rate at which capital extracts value from productive labor. It is a pure ratio of two derived/aggregate series, and per the Anu Extension Standard must be recomputed from extended components, NOT growth-rate spliced. Conceptual continuity holds as long as the numerator and denominator are extended with their Marxian definitions intact.", "vintage_note": "Inherits vintage divergences from S505 and S504. As a ratio, dimensionless, so unit-vintage issues cancel.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
+          <t>S506-COMBINED</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>provenance</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>{"shaikh_source": "Shaikh, A., &amp; Tonak, E. A. (1994). *Measuring the Wealth of Nations: The Political Economy of National Accounts*. Cambridge University Press., Chapter 5, Table 5.7 (rate of surplus value e = S*/V*); identity from Appendix H.1 series", "shaikh_appendix_ref": "Table 5.7 (rate of surplus value, 1948-1989); Appendix H.1 (S_star, V_star); Figure 5.6", "extension_source": "Derived ratio: e = S505 / S504. Inherits sources from S505 and S504 (which in turn depend on BLS CES + BEA NIPA).", "extension_url": "n/a (derived from S505 and S504)", "conceptual_continuity": "Rate of exploitation e = S*/V* is the Marxian ratio of surplus value to variable capital -- the rate at which capital extracts value from productive labor. It is a pure ratio of two derived/aggregate series, and per the Anu Extension Standard must be recomputed from extended components, NOT growth-rate spliced. Conceptual continuity holds as long as the numerator and denominator are extended with their Marxian definitions intact.", "vintage_note": "Inherits vintage divergences from S505 and S504. As a ratio, dimensionless, so unit-vintage issues cancel.", "note": "Hyper-review cleanup 2026-05-19 per Decision 0003"}</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>depends_on</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>["data/source/bea_sic/GDPbyInd_partitionA_SIC_1987_1997.csv", "gdp_by_industry_va_components.csv", "nipa_6_2D_compensation_by_industry.csv", "nipa_T20100_compensation_1929_2025.csv"]</t>
         </is>
       </c>
     </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>VALIDATION</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-    </row>
+    <row r="17"/>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>reference_values</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>{"1948": 1.7, "1958": 2.01, "1967": 2.1, "1972": 1.99, "1977": 2.1, "1989": 2.44}</t>
-        </is>
-      </c>
+          <t>VALIDATION</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>expected_range</t>
+          <t>reference_values</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>[1.0, 5.0]</t>
+          <t>{"1948": 1.7, "1958": 2.01, "1967": 2.1, "1972": 1.99, "1977": 2.1, "1989": 2.44}</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>tolerance</t>
+          <t>expected_range</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>rate_series</t>
+          <t>[1.0, 5.0]</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>tolerance_class</t>
+          <t>tolerance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3603,48 +3882,72 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>tolerance_rel</t>
+          <t>tolerance_class</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0.001</t>
+          <t>rate_series</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>tolerance_abs</t>
+          <t>tolerance_rel</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.001</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>extension_year_range</t>
+          <t>tolerance_abs</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>[1948, 2024]</t>
+          <t>0.01</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>extension_year_range</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>[1948, 2024]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
           <t>extension_reference_values</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>{"S506-EXT": {"1997": 0.8021, "1998": 0.7891, "2024": 1.1471}, "S506-EXT-OLD-DEPRECATED": {"1998": 1.27}}</t>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>{"S506-EXT": {"1997": 0.8021, "1998": 0.7891, "2024": 1.1471}, "S506-EXT-OLD-DEPRECATED": {"1998": 1.27}, "S506-EXT-MARX-KIO": {"1990": 2.4335, "1998": 2.9659, "2024": 4.4551}, "S506-COMBINED": {"1989": 2.44, "1990": 2.4335, "2024": 4.4551}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>kio_anchors</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>{"1989_frozen_exact": {"value": 1.5714, "note": "kIO_frozen = GFP*_1989/VA_partA_1989(SIC) = 4363.57/2776.843 = 1.5714 (book x BEA SIC, two independent sources)"}, "1992_native_mid": {"value": 1.5696, "band": [1.529, 1.61], "tol_rel": 0.005, "note": "B1 native 1992 SIC benchmark mid; splice central 1992 must be within 0.5% and inside the band (independent of B2)"}, "benchmark_years": [1997, 2002, 2007, 2012, 2017], "e_rescale_identity_tol": 1e-06, "source": "data/source/kio_reconstruction/kio_final_1990_2024.csv + data/final/S506_KIO_BAND.csv; Build/KIO_2026-07/{B1,B2,C}"}</t>
         </is>
       </c>
     </row>
